--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q140"/>
+  <dimension ref="A1:S140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,55 +453,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -535,29 +545,35 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>171.57</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>515</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>48</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -587,29 +603,35 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>-91</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>15</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>16</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>11.25</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>180</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>41</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -639,29 +661,35 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>137</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="n">
         <v>14</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>12.42</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>149</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>38</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -691,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -700,20 +728,26 @@
         <v>6</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>20</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>120</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>35</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -743,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -752,20 +786,26 @@
         <v>6</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>18</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>108</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>36</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -795,29 +835,35 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>14.36</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>86</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>45</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -842,29 +888,35 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>71</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>13</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>78</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>46</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -889,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -898,20 +950,26 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
         <v>13.84</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>55</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>41</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -936,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -945,20 +1003,26 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>21.37</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>21</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>39</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -983,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -992,24 +1056,30 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>11.18</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>36</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: Mar, Jun, Aug, Nov, Dec)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -1038,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1047,20 +1117,26 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
         <v>10.5</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>34</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1090,29 +1166,35 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
+        <v>200</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>17</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>18</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>39.74</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>715</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1142,29 +1224,35 @@
         <v>0.1</v>
       </c>
       <c r="G14" t="n">
+        <v>197</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>105</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>120</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.67</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>80</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1194,29 +1282,35 @@
         <v>0.3</v>
       </c>
       <c r="G15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I15" t="n">
         <v>13</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>9</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>108</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>40</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1246,29 +1340,35 @@
         <v>0.4</v>
       </c>
       <c r="G16" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I16" t="n">
         <v>9</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>12</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>9</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>108</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>40</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1298,29 +1398,35 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
+        <v>85</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>22</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>24</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>46.33</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>1112</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>43</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1350,29 +1456,35 @@
         <v>0.7</v>
       </c>
       <c r="G18" t="n">
+        <v>199</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
         <v>183</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>15</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>168</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>28</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>55.66</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>9351</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>99</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Margin over 95% - check retail; Large buy ($9,351) - confirm</t>
         </is>
@@ -1406,29 +1518,35 @@
         <v>0.7</v>
       </c>
       <c r="G19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>13</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>12</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>43</v>
-      </c>
-      <c r="L19" t="n">
-        <v>516</v>
       </c>
       <c r="M19" t="n">
         <v>43</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>516</v>
+      </c>
+      <c r="O19" t="n">
+        <v>43</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1453,7 +1571,7 @@
         <v>0.7</v>
       </c>
       <c r="G20" t="n">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1462,20 +1580,26 @@
         <v>33</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>33</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
+        <v>33</v>
+      </c>
+      <c r="M20" t="n">
         <v>1.25</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>41</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>45</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1505,33 +1629,39 @@
         <v>0.9</v>
       </c>
       <c r="G21" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I21" t="n">
         <v>53</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>48</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>8</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>21.11</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>1013</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>41</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>In buy-month (Feb, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1561,29 +1691,35 @@
         <v>0.9</v>
       </c>
       <c r="G22" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I22" t="n">
         <v>15</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>12</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>8.82</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>106</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>37</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1613,29 +1749,35 @@
         <v>0.9</v>
       </c>
       <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>6</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>12.58</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>75</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>30</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1665,7 +1807,7 @@
         <v>1.1</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1674,20 +1816,26 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>24</v>
+      </c>
+      <c r="L24" t="n">
         <v>8</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>15</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>360</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>32</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1717,29 +1865,35 @@
         <v>1.1</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I25" t="n">
         <v>6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>32.7</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>196</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>32</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1769,29 +1923,35 @@
         <v>1.1</v>
       </c>
       <c r="G26" t="n">
+        <v>33</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I26" t="n">
         <v>11</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>12.32</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>148</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>35</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1821,29 +1981,35 @@
         <v>1.1</v>
       </c>
       <c r="G27" t="n">
+        <v>71</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>6</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>12.58</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>75</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>30</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1873,29 +2039,35 @@
         <v>1.2</v>
       </c>
       <c r="G28" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="I28" t="n">
         <v>370</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>42</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>330</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>55</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>2.79</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>921</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>86</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1920,29 +2092,35 @@
         <v>1.2</v>
       </c>
       <c r="G29" t="n">
+        <v>25</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I29" t="n">
         <v>77</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>78</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>26</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>15</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>1170</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>32</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1972,29 +2150,35 @@
         <v>1.2</v>
       </c>
       <c r="G30" t="n">
+        <v>25</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I30" t="n">
         <v>29</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>30</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>5</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>22.9</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>687</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>35</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2024,29 +2208,35 @@
         <v>1.2</v>
       </c>
       <c r="G31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I31" t="n">
         <v>24</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>4</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>18</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>3</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>21.51</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>387</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>26</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2076,29 +2266,35 @@
         <v>1.2</v>
       </c>
       <c r="G32" t="n">
+        <v>31</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>6</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>183.05</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>1098</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>-281</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -2132,29 +2328,35 @@
         <v>1.3</v>
       </c>
       <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="I33" t="n">
         <v>249</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>4</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>246</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>41</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>2202</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>40</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2184,33 +2386,39 @@
         <v>1.3</v>
       </c>
       <c r="G34" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I34" t="n">
         <v>48</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>48</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>12.2</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>585</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>49</v>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>In buy-month (Feb, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2240,7 +2448,7 @@
         <v>1.3</v>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2249,20 +2457,26 @@
         <v>12</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>12</v>
+      </c>
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>100</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -2296,29 +2510,35 @@
         <v>1.3</v>
       </c>
       <c r="G36" t="n">
+        <v>55</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>11</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>12</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>2</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>13.33</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>160</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>41</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2348,33 +2568,39 @@
         <v>1.4</v>
       </c>
       <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="I37" t="n">
         <v>264</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>252</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>21</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>8.31</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>2095</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>36</v>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2404,29 +2630,35 @@
         <v>1.4</v>
       </c>
       <c r="G38" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>48</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>48</v>
+      </c>
+      <c r="L38" t="n">
         <v>8</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>11.88</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>570</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>41</v>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2456,7 +2688,7 @@
         <v>1.4</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2465,20 +2697,26 @@
         <v>6</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>22</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>132</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>44</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2508,29 +2746,35 @@
         <v>1.5</v>
       </c>
       <c r="G40" t="n">
+        <v>31</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I40" t="n">
         <v>325</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>4</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>324</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>27</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>15.31</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>4961</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>36</v>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
         <is>
           <t>Large buy ($4,961) - confirm</t>
         </is>
@@ -2564,29 +2808,35 @@
         <v>1.5</v>
       </c>
       <c r="G41" t="n">
+        <v>28</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>38</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>4</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>36</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>6</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>23.95</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>862</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>28</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2616,29 +2866,35 @@
         <v>1.6</v>
       </c>
       <c r="G42" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I42" t="n">
         <v>28</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>8</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>18</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>3</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>32.25</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>580</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>31</v>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2668,29 +2924,35 @@
         <v>1.6</v>
       </c>
       <c r="G43" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I43" t="n">
         <v>14</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>12</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>2</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>13.49</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>162</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>39</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2720,29 +2982,35 @@
         <v>1.7</v>
       </c>
       <c r="G44" t="n">
+        <v>36</v>
+      </c>
+      <c r="H44" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" t="n">
         <v>91</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>20</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>72</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>6</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>648</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>40</v>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2772,29 +3040,35 @@
         <v>1.8</v>
       </c>
       <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I45" t="n">
         <v>7</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>6</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>15</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>90</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>32</v>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2824,29 +3098,35 @@
         <v>1.8</v>
       </c>
       <c r="G46" t="n">
+        <v>9</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I46" t="n">
         <v>19</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>5</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>12</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>3.75</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>45</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>46</v>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2876,33 +3156,39 @@
         <v>1.9</v>
       </c>
       <c r="G47" t="n">
+        <v>25</v>
+      </c>
+      <c r="H47" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I47" t="n">
         <v>56</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>4</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>54</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>9</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>23.25</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>1255</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>34</v>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: Mar, Jun, Sep, Dec)</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -2936,33 +3222,39 @@
         <v>1.9</v>
       </c>
       <c r="G48" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>22</v>
+      </c>
+      <c r="I48" t="n">
         <v>23</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>24</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>8</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>15.18</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>364</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>31</v>
       </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>In buy-month (Jun, Jul, Aug)</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2987,29 +3279,35 @@
         <v>2</v>
       </c>
       <c r="G49" t="n">
+        <v>17</v>
+      </c>
+      <c r="H49" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="I49" t="n">
         <v>613</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>167</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>456</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>19</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>1.24</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>566</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>72</v>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3039,29 +3337,35 @@
         <v>2</v>
       </c>
       <c r="G50" t="n">
+        <v>22</v>
+      </c>
+      <c r="H50" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="I50" t="n">
         <v>168</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>19</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>144</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>12</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>19.92</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>2868</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>29</v>
       </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3091,29 +3395,35 @@
         <v>2</v>
       </c>
       <c r="G51" t="n">
+        <v>7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I51" t="n">
         <v>106</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>12</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>96</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>16</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>31.5</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>3024</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>17</v>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3143,29 +3453,35 @@
         <v>2</v>
       </c>
       <c r="G52" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I52" t="n">
         <v>54</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>4</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>48</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>8</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>467</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>44</v>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3195,29 +3511,35 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H53" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I53" t="n">
         <v>15</v>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>5</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>12</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>2</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>9</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>108</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>44</v>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3247,29 +3569,35 @@
         <v>2.1</v>
       </c>
       <c r="G54" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" t="n">
+        <v>55</v>
+      </c>
+      <c r="I54" t="n">
         <v>110</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>8</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>102</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>17</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>14.48</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>1477</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>44</v>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3299,29 +3627,35 @@
         <v>2.1</v>
       </c>
       <c r="G55" t="n">
+        <v>33</v>
+      </c>
+      <c r="H55" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I55" t="n">
         <v>97</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>28</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>72</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>12</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>2.63</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>189</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>85</v>
       </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3351,29 +3685,35 @@
         <v>2.1</v>
       </c>
       <c r="G56" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I56" t="n">
         <v>11</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>12</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>29.31</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>352</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>44</v>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3403,29 +3743,35 @@
         <v>2.1</v>
       </c>
       <c r="G57" t="n">
+        <v>110</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>8</v>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>9</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>3</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>15</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>135</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>32</v>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3455,29 +3801,35 @@
         <v>2.1</v>
       </c>
       <c r="G58" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="n">
         <v>4</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>6</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>21.73</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>130</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>43</v>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3507,29 +3859,35 @@
         <v>2.1</v>
       </c>
       <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I59" t="n">
         <v>5</v>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>6</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>25.42</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>153</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>28</v>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3559,29 +3917,35 @@
         <v>2.1</v>
       </c>
       <c r="G60" t="n">
+        <v>20</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
         <v>4</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>6</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>12.92</v>
       </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
         <v>78</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>38</v>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3611,29 +3975,35 @@
         <v>2.2</v>
       </c>
       <c r="G61" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>75</v>
+      </c>
+      <c r="I61" t="n">
         <v>202</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>39</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>162</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>27</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>16</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>2592</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>33</v>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3663,29 +4033,35 @@
         <v>2.2</v>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>35</v>
+      </c>
+      <c r="I62" t="n">
         <v>91</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>18</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>72</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>6</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
         <v>4.5</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>324</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>44</v>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3715,29 +4091,35 @@
         <v>2.2</v>
       </c>
       <c r="G63" t="n">
+        <v>27</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>22</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>6</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>24</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>2.14</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>51</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>57</v>
       </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3767,29 +4149,35 @@
         <v>2.3</v>
       </c>
       <c r="G64" t="n">
+        <v>14</v>
+      </c>
+      <c r="H64" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I64" t="n">
         <v>72</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>8</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>66</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>11</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
         <v>30.81</v>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
         <v>2033</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>25</v>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3819,29 +4207,35 @@
         <v>2.3</v>
       </c>
       <c r="G65" t="n">
+        <v>17</v>
+      </c>
+      <c r="H65" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I65" t="n">
         <v>31</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>30</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>5</v>
       </c>
-      <c r="K65" t="n">
+      <c r="M65" t="n">
         <v>41.67</v>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
         <v>1250</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>32</v>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3871,29 +4265,35 @@
         <v>2.3</v>
       </c>
       <c r="G66" t="n">
+        <v>200</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
         <v>10</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>5</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>6</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>22.5</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>135</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>36</v>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3923,29 +4323,35 @@
         <v>2.3</v>
       </c>
       <c r="G67" t="n">
-        <v>12</v>
+        <v>-19</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I67" t="n">
         <v>12</v>
       </c>
       <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>12</v>
+      </c>
+      <c r="L67" t="n">
         <v>2</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
         <v>10.04</v>
       </c>
-      <c r="L67" t="n">
+      <c r="N67" t="n">
         <v>120</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>43</v>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3975,29 +4381,35 @@
         <v>2.3</v>
       </c>
       <c r="G68" t="n">
+        <v>70</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>8</v>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>9</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>3</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
         <v>15</v>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>135</v>
       </c>
-      <c r="M68" t="n">
+      <c r="O68" t="n">
         <v>32</v>
       </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4027,29 +4439,35 @@
         <v>2.4</v>
       </c>
       <c r="G69" t="n">
+        <v>11</v>
+      </c>
+      <c r="H69" t="n">
+        <v>35</v>
+      </c>
+      <c r="I69" t="n">
         <v>110</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>28</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>84</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>7</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
         <v>15.31</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>1286</v>
       </c>
-      <c r="M69" t="n">
+      <c r="O69" t="n">
         <v>36</v>
       </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4079,29 +4497,35 @@
         <v>2.4</v>
       </c>
       <c r="G70" t="n">
+        <v>22</v>
+      </c>
+      <c r="H70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I70" t="n">
         <v>45</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>12</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>36</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>6</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
         <v>65.36</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>2353</v>
       </c>
-      <c r="M70" t="n">
+      <c r="O70" t="n">
         <v>20</v>
       </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4131,33 +4555,39 @@
         <v>2.4</v>
       </c>
       <c r="G71" t="n">
+        <v>39</v>
+      </c>
+      <c r="H71" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I71" t="n">
         <v>38</v>
       </c>
-      <c r="H71" t="n">
+      <c r="J71" t="n">
         <v>4</v>
       </c>
-      <c r="I71" t="n">
+      <c r="K71" t="n">
         <v>36</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>6</v>
       </c>
-      <c r="K71" t="n">
+      <c r="M71" t="n">
         <v>34.76</v>
       </c>
-      <c r="L71" t="n">
+      <c r="N71" t="n">
         <v>1251</v>
       </c>
-      <c r="M71" t="n">
+      <c r="O71" t="n">
         <v>29</v>
       </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
         <is>
           <t>In buy-month (Feb, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4187,33 +4617,39 @@
         <v>2.4</v>
       </c>
       <c r="G72" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H72" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I72" t="n">
         <v>25</v>
       </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>24</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>4</v>
       </c>
-      <c r="K72" t="n">
+      <c r="M72" t="n">
         <v>17.5</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>420</v>
       </c>
-      <c r="M72" t="n">
+      <c r="O72" t="n">
         <v>35</v>
       </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
         <is>
           <t>In buy-month (May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4243,29 +4679,35 @@
         <v>2.4</v>
       </c>
       <c r="G73" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I73" t="n">
         <v>13</v>
       </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>12</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>2</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
         <v>12.92</v>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
         <v>155</v>
       </c>
-      <c r="M73" t="n">
+      <c r="O73" t="n">
         <v>46</v>
       </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4295,29 +4737,35 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
+        <v>10</v>
+      </c>
+      <c r="H74" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="I74" t="n">
         <v>108</v>
       </c>
-      <c r="H74" t="n">
+      <c r="J74" t="n">
         <v>28</v>
       </c>
-      <c r="I74" t="n">
+      <c r="K74" t="n">
         <v>84</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>7</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
         <v>22.5</v>
       </c>
-      <c r="L74" t="n">
+      <c r="N74" t="n">
         <v>1890</v>
       </c>
-      <c r="M74" t="n">
+      <c r="O74" t="n">
         <v>30</v>
       </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4347,29 +4795,35 @@
         <v>2.5</v>
       </c>
       <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="n">
+        <v>35</v>
+      </c>
+      <c r="I75" t="n">
         <v>62</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>5</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>60</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>10</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
         <v>13.06</v>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
         <v>784</v>
       </c>
-      <c r="M75" t="n">
+      <c r="O75" t="n">
         <v>35</v>
       </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4399,29 +4853,35 @@
         <v>2.6</v>
       </c>
       <c r="G76" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3324.5</v>
+      </c>
+      <c r="I76" t="n">
         <v>6496</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>2018</v>
       </c>
-      <c r="I76" t="n">
+      <c r="K76" t="n">
         <v>4440</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>37</v>
       </c>
-      <c r="K76" t="n">
+      <c r="M76" t="n">
         <v>0.52</v>
       </c>
-      <c r="L76" t="n">
+      <c r="N76" t="n">
         <v>2325</v>
       </c>
-      <c r="M76" t="n">
+      <c r="O76" t="n">
         <v>65</v>
       </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4451,29 +4911,35 @@
         <v>2.6</v>
       </c>
       <c r="G77" t="n">
+        <v>23</v>
+      </c>
+      <c r="H77" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I77" t="n">
         <v>81</v>
       </c>
-      <c r="H77" t="n">
+      <c r="J77" t="n">
         <v>31</v>
       </c>
-      <c r="I77" t="n">
+      <c r="K77" t="n">
         <v>48</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>4</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
         <v>10.45</v>
       </c>
-      <c r="L77" t="n">
+      <c r="N77" t="n">
         <v>501</v>
       </c>
-      <c r="M77" t="n">
+      <c r="O77" t="n">
         <v>42</v>
       </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4503,29 +4969,35 @@
         <v>2.6</v>
       </c>
       <c r="G78" t="n">
+        <v>100</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
         <v>115</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>34</v>
       </c>
-      <c r="I78" t="n">
+      <c r="K78" t="n">
         <v>81</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>27</v>
       </c>
-      <c r="K78" t="n">
+      <c r="M78" t="n">
         <v>13.5</v>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
         <v>1094</v>
       </c>
-      <c r="M78" t="n">
+      <c r="O78" t="n">
         <v>25</v>
       </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4555,29 +5027,35 @@
         <v>2.6</v>
       </c>
       <c r="G79" t="n">
+        <v>122</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
         <v>69</v>
       </c>
-      <c r="H79" t="n">
+      <c r="J79" t="n">
         <v>27</v>
       </c>
-      <c r="I79" t="n">
+      <c r="K79" t="n">
         <v>42</v>
       </c>
-      <c r="J79" t="n">
+      <c r="L79" t="n">
         <v>14</v>
       </c>
-      <c r="K79" t="n">
+      <c r="M79" t="n">
         <v>13.29</v>
       </c>
-      <c r="L79" t="n">
+      <c r="N79" t="n">
         <v>558</v>
       </c>
-      <c r="M79" t="n">
+      <c r="O79" t="n">
         <v>34</v>
       </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4607,29 +5085,35 @@
         <v>2.6</v>
       </c>
       <c r="G80" t="n">
+        <v>20</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I80" t="n">
         <v>8</v>
       </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>6</v>
       </c>
-      <c r="J80" t="n">
+      <c r="L80" t="n">
         <v>1</v>
       </c>
-      <c r="K80" t="n">
+      <c r="M80" t="n">
         <v>11.24</v>
       </c>
-      <c r="L80" t="n">
+      <c r="N80" t="n">
         <v>67</v>
       </c>
-      <c r="M80" t="n">
+      <c r="O80" t="n">
         <v>53</v>
       </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4659,29 +5143,35 @@
         <v>2.7</v>
       </c>
       <c r="G81" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H81" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I81" t="n">
         <v>78</v>
       </c>
-      <c r="H81" t="n">
+      <c r="J81" t="n">
         <v>24</v>
       </c>
-      <c r="I81" t="n">
+      <c r="K81" t="n">
         <v>54</v>
       </c>
-      <c r="J81" t="n">
+      <c r="L81" t="n">
         <v>9</v>
       </c>
-      <c r="K81" t="n">
+      <c r="M81" t="n">
         <v>25.67</v>
       </c>
-      <c r="L81" t="n">
+      <c r="N81" t="n">
         <v>1386</v>
       </c>
-      <c r="M81" t="n">
+      <c r="O81" t="n">
         <v>34</v>
       </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4711,29 +5201,35 @@
         <v>2.7</v>
       </c>
       <c r="G82" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H82" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I82" t="n">
         <v>41</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>5</v>
       </c>
-      <c r="I82" t="n">
+      <c r="K82" t="n">
         <v>36</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>6</v>
       </c>
-      <c r="K82" t="n">
+      <c r="M82" t="n">
         <v>19.78</v>
       </c>
-      <c r="L82" t="n">
+      <c r="N82" t="n">
         <v>712</v>
       </c>
-      <c r="M82" t="n">
+      <c r="O82" t="n">
         <v>40</v>
       </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4763,29 +5259,35 @@
         <v>2.7</v>
       </c>
       <c r="G83" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H83" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I83" t="n">
         <v>75</v>
       </c>
-      <c r="H83" t="n">
+      <c r="J83" t="n">
         <v>24</v>
       </c>
-      <c r="I83" t="n">
+      <c r="K83" t="n">
         <v>48</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>4</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="L83" t="n">
+      <c r="N83" t="n">
         <v>430</v>
       </c>
-      <c r="M83" t="n">
+      <c r="O83" t="n">
         <v>47</v>
       </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4815,29 +5317,35 @@
         <v>2.7</v>
       </c>
       <c r="G84" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H84" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I84" t="n">
         <v>42</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>19</v>
       </c>
-      <c r="I84" t="n">
+      <c r="K84" t="n">
         <v>24</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>4</v>
       </c>
-      <c r="K84" t="n">
+      <c r="M84" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="L84" t="n">
+      <c r="N84" t="n">
         <v>211</v>
       </c>
-      <c r="M84" t="n">
+      <c r="O84" t="n">
         <v>41</v>
       </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4867,33 +5375,39 @@
         <v>2.7</v>
       </c>
       <c r="G85" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I85" t="n">
         <v>10</v>
       </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
         <v>12</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>2</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
         <v>15.46</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>186</v>
       </c>
-      <c r="M85" t="n">
+      <c r="O85" t="n">
         <v>34</v>
       </c>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
         <is>
           <t>In buy-month (May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4923,29 +5437,35 @@
         <v>2.7</v>
       </c>
       <c r="G86" t="n">
+        <v>20</v>
+      </c>
+      <c r="H86" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="I86" t="n">
         <v>96</v>
       </c>
-      <c r="H86" t="n">
+      <c r="J86" t="n">
         <v>21</v>
       </c>
-      <c r="I86" t="n">
+      <c r="K86" t="n">
         <v>72</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>6</v>
       </c>
-      <c r="K86" t="n">
+      <c r="M86" t="n">
         <v>112.79</v>
       </c>
-      <c r="L86" t="n">
+      <c r="N86" t="n">
         <v>8121</v>
       </c>
-      <c r="M86" t="n">
+      <c r="O86" t="n">
         <v>-169</v>
       </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost; Large buy ($8,121) - confirm</t>
         </is>
@@ -4979,29 +5499,35 @@
         <v>2.8</v>
       </c>
       <c r="G87" t="n">
+        <v>17</v>
+      </c>
+      <c r="H87" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I87" t="n">
         <v>53</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>15</v>
       </c>
-      <c r="I87" t="n">
+      <c r="K87" t="n">
         <v>36</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>6</v>
       </c>
-      <c r="K87" t="n">
+      <c r="M87" t="n">
         <v>16.98</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>611</v>
       </c>
-      <c r="M87" t="n">
+      <c r="O87" t="n">
         <v>61</v>
       </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5031,29 +5557,35 @@
         <v>2.8</v>
       </c>
       <c r="G88" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" t="n">
+        <v>23</v>
+      </c>
+      <c r="I88" t="n">
         <v>77</v>
       </c>
-      <c r="H88" t="n">
+      <c r="J88" t="n">
         <v>27</v>
       </c>
-      <c r="I88" t="n">
+      <c r="K88" t="n">
         <v>48</v>
       </c>
-      <c r="J88" t="n">
+      <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="K88" t="n">
+      <c r="M88" t="n">
         <v>14.12</v>
       </c>
-      <c r="L88" t="n">
+      <c r="N88" t="n">
         <v>678</v>
       </c>
-      <c r="M88" t="n">
+      <c r="O88" t="n">
         <v>46</v>
       </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5083,29 +5615,35 @@
         <v>2.8</v>
       </c>
       <c r="G89" t="n">
+        <v>35</v>
+      </c>
+      <c r="H89" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I89" t="n">
         <v>60</v>
       </c>
-      <c r="H89" t="n">
+      <c r="J89" t="n">
         <v>27</v>
       </c>
-      <c r="I89" t="n">
+      <c r="K89" t="n">
         <v>36</v>
       </c>
-      <c r="J89" t="n">
+      <c r="L89" t="n">
         <v>6</v>
       </c>
-      <c r="K89" t="n">
+      <c r="M89" t="n">
         <v>12.13</v>
       </c>
-      <c r="L89" t="n">
+      <c r="N89" t="n">
         <v>437</v>
       </c>
-      <c r="M89" t="n">
+      <c r="O89" t="n">
         <v>49</v>
       </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5135,29 +5673,35 @@
         <v>2.8</v>
       </c>
       <c r="G90" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H90" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I90" t="n">
         <v>29</v>
       </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>30</v>
       </c>
-      <c r="J90" t="n">
+      <c r="L90" t="n">
         <v>5</v>
       </c>
-      <c r="K90" t="n">
+      <c r="M90" t="n">
         <v>43.91</v>
       </c>
-      <c r="L90" t="n">
+      <c r="N90" t="n">
         <v>1317</v>
       </c>
-      <c r="M90" t="n">
+      <c r="O90" t="n">
         <v>32</v>
       </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5187,29 +5731,35 @@
         <v>2.8</v>
       </c>
       <c r="G91" t="n">
+        <v>13</v>
+      </c>
+      <c r="H91" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I91" t="n">
         <v>83</v>
       </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
         <v>45</v>
       </c>
-      <c r="I91" t="n">
+      <c r="K91" t="n">
         <v>36</v>
       </c>
-      <c r="J91" t="n">
+      <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="K91" t="n">
+      <c r="M91" t="n">
         <v>4.82</v>
       </c>
-      <c r="L91" t="n">
+      <c r="N91" t="n">
         <v>173</v>
       </c>
-      <c r="M91" t="n">
+      <c r="O91" t="n">
         <v>46</v>
       </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5239,29 +5789,35 @@
         <v>2.9</v>
       </c>
       <c r="G92" t="n">
+        <v>14</v>
+      </c>
+      <c r="H92" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="I92" t="n">
         <v>177</v>
       </c>
-      <c r="H92" t="n">
+      <c r="J92" t="n">
         <v>61</v>
       </c>
-      <c r="I92" t="n">
+      <c r="K92" t="n">
         <v>120</v>
       </c>
-      <c r="J92" t="n">
+      <c r="L92" t="n">
         <v>5</v>
       </c>
-      <c r="K92" t="n">
+      <c r="M92" t="n">
         <v>2.91</v>
       </c>
-      <c r="L92" t="n">
+      <c r="N92" t="n">
         <v>349</v>
       </c>
-      <c r="M92" t="n">
+      <c r="O92" t="n">
         <v>64</v>
       </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5291,29 +5847,35 @@
         <v>2.9</v>
       </c>
       <c r="G93" t="n">
+        <v>4</v>
+      </c>
+      <c r="H93" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I93" t="n">
         <v>88</v>
       </c>
-      <c r="H93" t="n">
+      <c r="J93" t="n">
         <v>47</v>
       </c>
-      <c r="I93" t="n">
+      <c r="K93" t="n">
         <v>48</v>
       </c>
-      <c r="J93" t="n">
+      <c r="L93" t="n">
         <v>2</v>
       </c>
-      <c r="K93" t="n">
+      <c r="M93" t="n">
         <v>4.58</v>
       </c>
-      <c r="L93" t="n">
+      <c r="N93" t="n">
         <v>220</v>
       </c>
-      <c r="M93" t="n">
+      <c r="O93" t="n">
         <v>34</v>
       </c>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5343,29 +5905,35 @@
         <v>3</v>
       </c>
       <c r="G94" t="n">
+        <v>6</v>
+      </c>
+      <c r="H94" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="I94" t="n">
         <v>224</v>
       </c>
-      <c r="H94" t="n">
+      <c r="J94" t="n">
         <v>37</v>
       </c>
-      <c r="I94" t="n">
+      <c r="K94" t="n">
         <v>186</v>
       </c>
-      <c r="J94" t="n">
+      <c r="L94" t="n">
         <v>31</v>
       </c>
-      <c r="K94" t="n">
+      <c r="M94" t="n">
         <v>14.58</v>
       </c>
-      <c r="L94" t="n">
+      <c r="N94" t="n">
         <v>2713</v>
       </c>
-      <c r="M94" t="n">
+      <c r="O94" t="n">
         <v>39</v>
       </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5395,29 +5963,35 @@
         <v>3</v>
       </c>
       <c r="G95" t="n">
+        <v>11</v>
+      </c>
+      <c r="H95" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="I95" t="n">
         <v>752</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>212</v>
       </c>
-      <c r="I95" t="n">
+      <c r="K95" t="n">
         <v>576</v>
       </c>
-      <c r="J95" t="n">
+      <c r="L95" t="n">
         <v>8</v>
       </c>
-      <c r="K95" t="n">
+      <c r="M95" t="n">
         <v>0.68</v>
       </c>
-      <c r="L95" t="n">
+      <c r="N95" t="n">
         <v>391</v>
       </c>
-      <c r="M95" t="n">
+      <c r="O95" t="n">
         <v>54</v>
       </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5447,29 +6021,35 @@
         <v>3</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I96" t="n">
         <v>65</v>
       </c>
-      <c r="H96" t="n">
+      <c r="J96" t="n">
         <v>26</v>
       </c>
-      <c r="I96" t="n">
+      <c r="K96" t="n">
         <v>36</v>
       </c>
-      <c r="J96" t="n">
+      <c r="L96" t="n">
         <v>6</v>
       </c>
-      <c r="K96" t="n">
+      <c r="M96" t="n">
         <v>12.01</v>
       </c>
-      <c r="L96" t="n">
+      <c r="N96" t="n">
         <v>432</v>
       </c>
-      <c r="M96" t="n">
+      <c r="O96" t="n">
         <v>40</v>
       </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5499,29 +6079,35 @@
         <v>3</v>
       </c>
       <c r="G97" t="n">
+        <v>18</v>
+      </c>
+      <c r="H97" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I97" t="n">
         <v>63</v>
       </c>
-      <c r="H97" t="n">
+      <c r="J97" t="n">
         <v>22</v>
       </c>
-      <c r="I97" t="n">
+      <c r="K97" t="n">
         <v>36</v>
       </c>
-      <c r="J97" t="n">
+      <c r="L97" t="n">
         <v>3</v>
       </c>
-      <c r="K97" t="n">
+      <c r="M97" t="n">
         <v>5.48</v>
       </c>
-      <c r="L97" t="n">
+      <c r="N97" t="n">
         <v>197</v>
       </c>
-      <c r="M97" t="n">
+      <c r="O97" t="n">
         <v>52</v>
       </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5551,33 +6137,39 @@
         <v>3</v>
       </c>
       <c r="G98" t="n">
+        <v>27</v>
+      </c>
+      <c r="H98" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I98" t="n">
         <v>50</v>
       </c>
-      <c r="H98" t="n">
+      <c r="J98" t="n">
         <v>15</v>
       </c>
-      <c r="I98" t="n">
+      <c r="K98" t="n">
         <v>36</v>
       </c>
-      <c r="J98" t="n">
+      <c r="L98" t="n">
         <v>6</v>
       </c>
-      <c r="K98" t="n">
+      <c r="M98" t="n">
         <v>36.89</v>
       </c>
-      <c r="L98" t="n">
+      <c r="N98" t="n">
         <v>1328</v>
       </c>
-      <c r="M98" t="n">
+      <c r="O98" t="n">
         <v>23</v>
       </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5607,29 +6199,35 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
+        <v>34</v>
+      </c>
+      <c r="H99" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I99" t="n">
         <v>22</v>
       </c>
-      <c r="H99" t="n">
+      <c r="J99" t="n">
         <v>4</v>
       </c>
-      <c r="I99" t="n">
+      <c r="K99" t="n">
         <v>18</v>
       </c>
-      <c r="J99" t="n">
+      <c r="L99" t="n">
         <v>3</v>
       </c>
-      <c r="K99" t="n">
+      <c r="M99" t="n">
         <v>19.08</v>
       </c>
-      <c r="L99" t="n">
+      <c r="N99" t="n">
         <v>343</v>
       </c>
-      <c r="M99" t="n">
+      <c r="O99" t="n">
         <v>36</v>
       </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5659,29 +6257,35 @@
         <v>3</v>
       </c>
       <c r="G100" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="I100" t="n">
         <v>12</v>
       </c>
       <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>12</v>
+      </c>
+      <c r="L100" t="n">
         <v>2</v>
       </c>
-      <c r="K100" t="n">
+      <c r="M100" t="n">
         <v>17.83</v>
       </c>
-      <c r="L100" t="n">
+      <c r="N100" t="n">
         <v>214</v>
       </c>
-      <c r="M100" t="n">
+      <c r="O100" t="n">
         <v>36</v>
       </c>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5711,29 +6315,35 @@
         <v>3.1</v>
       </c>
       <c r="G101" t="n">
+        <v>20</v>
+      </c>
+      <c r="H101" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I101" t="n">
         <v>40</v>
       </c>
-      <c r="H101" t="n">
+      <c r="J101" t="n">
         <v>20</v>
       </c>
-      <c r="I101" t="n">
+      <c r="K101" t="n">
         <v>18</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>3</v>
       </c>
-      <c r="K101" t="n">
+      <c r="M101" t="n">
         <v>25.26</v>
       </c>
-      <c r="L101" t="n">
+      <c r="N101" t="n">
         <v>455</v>
       </c>
-      <c r="M101" t="n">
+      <c r="O101" t="n">
         <v>28</v>
       </c>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5763,29 +6373,35 @@
         <v>3.1</v>
       </c>
       <c r="G102" t="n">
+        <v>28</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
         <v>36</v>
       </c>
-      <c r="H102" t="n">
+      <c r="J102" t="n">
         <v>22</v>
       </c>
-      <c r="I102" t="n">
+      <c r="K102" t="n">
         <v>15</v>
       </c>
-      <c r="J102" t="n">
+      <c r="L102" t="n">
         <v>5</v>
       </c>
-      <c r="K102" t="n">
+      <c r="M102" t="n">
         <v>14.99</v>
       </c>
-      <c r="L102" t="n">
+      <c r="N102" t="n">
         <v>225</v>
       </c>
-      <c r="M102" t="n">
+      <c r="O102" t="n">
         <v>29</v>
       </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5815,29 +6431,35 @@
         <v>3.1</v>
       </c>
       <c r="G103" t="n">
+        <v>8</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
         <v>59</v>
       </c>
-      <c r="H103" t="n">
+      <c r="J103" t="n">
         <v>33</v>
       </c>
-      <c r="I103" t="n">
+      <c r="K103" t="n">
         <v>24</v>
       </c>
-      <c r="J103" t="n">
+      <c r="L103" t="n">
         <v>1</v>
       </c>
-      <c r="K103" t="n">
+      <c r="M103" t="n">
         <v>2.14</v>
       </c>
-      <c r="L103" t="n">
+      <c r="N103" t="n">
         <v>51</v>
       </c>
-      <c r="M103" t="n">
+      <c r="O103" t="n">
         <v>57</v>
       </c>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5867,29 +6489,35 @@
         <v>3.1</v>
       </c>
       <c r="G104" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H104" t="n">
+        <v>12</v>
+      </c>
+      <c r="I104" t="n">
         <v>23</v>
       </c>
-      <c r="H104" t="n">
+      <c r="J104" t="n">
         <v>4</v>
       </c>
-      <c r="I104" t="n">
+      <c r="K104" t="n">
         <v>18</v>
       </c>
-      <c r="J104" t="n">
+      <c r="L104" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="n">
+      <c r="M104" t="n">
         <v>16.07</v>
       </c>
-      <c r="L104" t="n">
+      <c r="N104" t="n">
         <v>289</v>
       </c>
-      <c r="M104" t="n">
+      <c r="O104" t="n">
         <v>33</v>
       </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5919,29 +6547,35 @@
         <v>3.1</v>
       </c>
       <c r="G105" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
         <v>12</v>
       </c>
-      <c r="H105" t="n">
+      <c r="J105" t="n">
         <v>4</v>
       </c>
-      <c r="I105" t="n">
+      <c r="K105" t="n">
         <v>6</v>
       </c>
-      <c r="J105" t="n">
+      <c r="L105" t="n">
         <v>1</v>
       </c>
-      <c r="K105" t="n">
+      <c r="M105" t="n">
         <v>33.74</v>
       </c>
-      <c r="L105" t="n">
+      <c r="N105" t="n">
         <v>202</v>
       </c>
-      <c r="M105" t="n">
+      <c r="O105" t="n">
         <v>36</v>
       </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5971,29 +6605,35 @@
         <v>3.1</v>
       </c>
       <c r="G106" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I106" t="n">
         <v>6</v>
       </c>
       <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>6</v>
+      </c>
+      <c r="L106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" t="n">
+      <c r="M106" t="n">
         <v>58.9</v>
       </c>
-      <c r="L106" t="n">
+      <c r="N106" t="n">
         <v>353</v>
       </c>
-      <c r="M106" t="n">
+      <c r="O106" t="n">
         <v>26</v>
       </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6023,29 +6663,35 @@
         <v>3.1</v>
       </c>
       <c r="G107" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I107" t="n">
         <v>6</v>
       </c>
       <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>6</v>
+      </c>
+      <c r="L107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" t="n">
+      <c r="M107" t="n">
         <v>30.75</v>
       </c>
-      <c r="L107" t="n">
+      <c r="N107" t="n">
         <v>185</v>
       </c>
-      <c r="M107" t="n">
+      <c r="O107" t="n">
         <v>37</v>
       </c>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6075,29 +6721,35 @@
         <v>3.1</v>
       </c>
       <c r="G108" t="n">
+        <v>24</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I108" t="n">
         <v>5</v>
       </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
         <v>6</v>
       </c>
-      <c r="J108" t="n">
+      <c r="L108" t="n">
         <v>1</v>
       </c>
-      <c r="K108" t="n">
+      <c r="M108" t="n">
         <v>22.5</v>
       </c>
-      <c r="L108" t="n">
+      <c r="N108" t="n">
         <v>135</v>
       </c>
-      <c r="M108" t="n">
+      <c r="O108" t="n">
         <v>37</v>
       </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6127,29 +6779,35 @@
         <v>3.2</v>
       </c>
       <c r="G109" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I109" t="n">
         <v>48</v>
       </c>
-      <c r="H109" t="n">
+      <c r="J109" t="n">
         <v>27</v>
       </c>
-      <c r="I109" t="n">
+      <c r="K109" t="n">
         <v>24</v>
       </c>
-      <c r="J109" t="n">
+      <c r="L109" t="n">
         <v>4</v>
       </c>
-      <c r="K109" t="n">
+      <c r="M109" t="n">
         <v>14.41</v>
       </c>
-      <c r="L109" t="n">
+      <c r="N109" t="n">
         <v>346</v>
       </c>
-      <c r="M109" t="n">
+      <c r="O109" t="n">
         <v>40</v>
       </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6179,33 +6837,39 @@
         <v>3.3</v>
       </c>
       <c r="G110" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>152</v>
+      </c>
+      <c r="I110" t="n">
         <v>190</v>
       </c>
-      <c r="H110" t="n">
+      <c r="J110" t="n">
         <v>87</v>
       </c>
-      <c r="I110" t="n">
+      <c r="K110" t="n">
         <v>102</v>
       </c>
-      <c r="J110" t="n">
+      <c r="L110" t="n">
         <v>17</v>
       </c>
-      <c r="K110" t="n">
+      <c r="M110" t="n">
         <v>14.18</v>
       </c>
-      <c r="L110" t="n">
+      <c r="N110" t="n">
         <v>1447</v>
       </c>
-      <c r="M110" t="n">
+      <c r="O110" t="n">
         <v>32</v>
       </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6235,29 +6899,35 @@
         <v>3.3</v>
       </c>
       <c r="G111" t="n">
+        <v>15</v>
+      </c>
+      <c r="H111" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I111" t="n">
         <v>51</v>
       </c>
-      <c r="H111" t="n">
+      <c r="J111" t="n">
         <v>28</v>
       </c>
-      <c r="I111" t="n">
+      <c r="K111" t="n">
         <v>24</v>
       </c>
-      <c r="J111" t="n">
+      <c r="L111" t="n">
         <v>4</v>
       </c>
-      <c r="K111" t="n">
+      <c r="M111" t="n">
         <v>5.32</v>
       </c>
-      <c r="L111" t="n">
+      <c r="N111" t="n">
         <v>128</v>
       </c>
-      <c r="M111" t="n">
+      <c r="O111" t="n">
         <v>70</v>
       </c>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6287,29 +6957,35 @@
         <v>3.3</v>
       </c>
       <c r="G112" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I112" t="n">
         <v>26</v>
-      </c>
-      <c r="H112" t="n">
-        <v>4</v>
-      </c>
-      <c r="I112" t="n">
-        <v>24</v>
       </c>
       <c r="J112" t="n">
         <v>4</v>
       </c>
       <c r="K112" t="n">
+        <v>24</v>
+      </c>
+      <c r="L112" t="n">
+        <v>4</v>
+      </c>
+      <c r="M112" t="n">
         <v>24.78</v>
       </c>
-      <c r="L112" t="n">
+      <c r="N112" t="n">
         <v>595</v>
       </c>
-      <c r="M112" t="n">
+      <c r="O112" t="n">
         <v>38</v>
       </c>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6339,29 +7015,35 @@
         <v>3.3</v>
       </c>
       <c r="G113" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I113" t="n">
         <v>30</v>
       </c>
-      <c r="H113" t="n">
+      <c r="J113" t="n">
         <v>15</v>
       </c>
-      <c r="I113" t="n">
+      <c r="K113" t="n">
         <v>12</v>
       </c>
-      <c r="J113" t="n">
+      <c r="L113" t="n">
         <v>2</v>
       </c>
-      <c r="K113" t="n">
+      <c r="M113" t="n">
         <v>25.25</v>
       </c>
-      <c r="L113" t="n">
+      <c r="N113" t="n">
         <v>303</v>
       </c>
-      <c r="M113" t="n">
+      <c r="O113" t="n">
         <v>38</v>
       </c>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6391,29 +7073,35 @@
         <v>3.3</v>
       </c>
       <c r="G114" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H114" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I114" t="n">
         <v>40</v>
       </c>
-      <c r="H114" t="n">
+      <c r="J114" t="n">
         <v>24</v>
       </c>
-      <c r="I114" t="n">
+      <c r="K114" t="n">
         <v>18</v>
       </c>
-      <c r="J114" t="n">
+      <c r="L114" t="n">
         <v>3</v>
       </c>
-      <c r="K114" t="n">
+      <c r="M114" t="n">
         <v>17.27</v>
       </c>
-      <c r="L114" t="n">
+      <c r="N114" t="n">
         <v>311</v>
       </c>
-      <c r="M114" t="n">
+      <c r="O114" t="n">
         <v>26</v>
       </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6443,29 +7131,35 @@
         <v>3.3</v>
       </c>
       <c r="G115" t="n">
+        <v>14</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n">
         <v>18</v>
       </c>
-      <c r="H115" t="n">
+      <c r="J115" t="n">
         <v>10</v>
       </c>
-      <c r="I115" t="n">
+      <c r="K115" t="n">
         <v>12</v>
       </c>
-      <c r="J115" t="n">
+      <c r="L115" t="n">
         <v>1</v>
       </c>
-      <c r="K115" t="n">
+      <c r="M115" t="n">
         <v>9.51</v>
       </c>
-      <c r="L115" t="n">
+      <c r="N115" t="n">
         <v>114</v>
       </c>
-      <c r="M115" t="n">
+      <c r="O115" t="n">
         <v>37</v>
       </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6495,29 +7189,35 @@
         <v>3.4</v>
       </c>
       <c r="G116" t="n">
+        <v>15</v>
+      </c>
+      <c r="H116" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I116" t="n">
         <v>195</v>
       </c>
-      <c r="H116" t="n">
+      <c r="J116" t="n">
         <v>123</v>
       </c>
-      <c r="I116" t="n">
+      <c r="K116" t="n">
         <v>72</v>
       </c>
-      <c r="J116" t="n">
+      <c r="L116" t="n">
         <v>3</v>
       </c>
-      <c r="K116" t="n">
+      <c r="M116" t="n">
         <v>5.1</v>
       </c>
-      <c r="L116" t="n">
+      <c r="N116" t="n">
         <v>367</v>
       </c>
-      <c r="M116" t="n">
+      <c r="O116" t="n">
         <v>43</v>
       </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6547,29 +7247,35 @@
         <v>3.4</v>
       </c>
       <c r="G117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I117" t="n">
         <v>28</v>
       </c>
-      <c r="H117" t="n">
+      <c r="J117" t="n">
         <v>11</v>
       </c>
-      <c r="I117" t="n">
+      <c r="K117" t="n">
         <v>18</v>
       </c>
-      <c r="J117" t="n">
+      <c r="L117" t="n">
         <v>3</v>
       </c>
-      <c r="K117" t="n">
+      <c r="M117" t="n">
         <v>15.82</v>
       </c>
-      <c r="L117" t="n">
+      <c r="N117" t="n">
         <v>285</v>
       </c>
-      <c r="M117" t="n">
+      <c r="O117" t="n">
         <v>37</v>
       </c>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6599,29 +7305,35 @@
         <v>3.4</v>
       </c>
       <c r="G118" t="n">
+        <v>15</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
         <v>17</v>
-      </c>
-      <c r="H118" t="n">
-        <v>4</v>
-      </c>
-      <c r="I118" t="n">
-        <v>12</v>
       </c>
       <c r="J118" t="n">
         <v>4</v>
       </c>
       <c r="K118" t="n">
+        <v>12</v>
+      </c>
+      <c r="L118" t="n">
+        <v>4</v>
+      </c>
+      <c r="M118" t="n">
         <v>15</v>
       </c>
-      <c r="L118" t="n">
+      <c r="N118" t="n">
         <v>180</v>
       </c>
-      <c r="M118" t="n">
+      <c r="O118" t="n">
         <v>37</v>
       </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6651,29 +7363,35 @@
         <v>3.4</v>
       </c>
       <c r="G119" t="n">
+        <v>16</v>
+      </c>
+      <c r="H119" t="n">
+        <v>5</v>
+      </c>
+      <c r="I119" t="n">
         <v>7</v>
       </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
         <v>6</v>
       </c>
-      <c r="J119" t="n">
+      <c r="L119" t="n">
         <v>1</v>
       </c>
-      <c r="K119" t="n">
+      <c r="M119" t="n">
         <v>22.5</v>
       </c>
-      <c r="L119" t="n">
+      <c r="N119" t="n">
         <v>135</v>
       </c>
-      <c r="M119" t="n">
+      <c r="O119" t="n">
         <v>37</v>
       </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6703,29 +7421,35 @@
         <v>3.5</v>
       </c>
       <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="I120" t="n">
         <v>91</v>
       </c>
-      <c r="H120" t="n">
+      <c r="J120" t="n">
         <v>41</v>
       </c>
-      <c r="I120" t="n">
+      <c r="K120" t="n">
         <v>48</v>
       </c>
-      <c r="J120" t="n">
+      <c r="L120" t="n">
         <v>8</v>
       </c>
-      <c r="K120" t="n">
+      <c r="M120" t="n">
         <v>17.15</v>
       </c>
-      <c r="L120" t="n">
+      <c r="N120" t="n">
         <v>823</v>
       </c>
-      <c r="M120" t="n">
+      <c r="O120" t="n">
         <v>28</v>
       </c>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6755,29 +7479,35 @@
         <v>3.6</v>
       </c>
       <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I121" t="n">
         <v>69</v>
       </c>
-      <c r="H121" t="n">
+      <c r="J121" t="n">
         <v>45</v>
       </c>
-      <c r="I121" t="n">
+      <c r="K121" t="n">
         <v>24</v>
       </c>
-      <c r="J121" t="n">
+      <c r="L121" t="n">
         <v>2</v>
       </c>
-      <c r="K121" t="n">
+      <c r="M121" t="n">
         <v>9</v>
       </c>
-      <c r="L121" t="n">
+      <c r="N121" t="n">
         <v>216</v>
       </c>
-      <c r="M121" t="n">
+      <c r="O121" t="n">
         <v>36</v>
       </c>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6807,29 +7537,35 @@
         <v>3.6</v>
       </c>
       <c r="G122" t="n">
+        <v>24</v>
+      </c>
+      <c r="H122" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I122" t="n">
         <v>33</v>
       </c>
-      <c r="H122" t="n">
+      <c r="J122" t="n">
         <v>20</v>
       </c>
-      <c r="I122" t="n">
+      <c r="K122" t="n">
         <v>12</v>
       </c>
-      <c r="J122" t="n">
+      <c r="L122" t="n">
         <v>2</v>
       </c>
-      <c r="K122" t="n">
+      <c r="M122" t="n">
         <v>24.21</v>
       </c>
-      <c r="L122" t="n">
+      <c r="N122" t="n">
         <v>291</v>
       </c>
-      <c r="M122" t="n">
+      <c r="O122" t="n">
         <v>35</v>
       </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6859,29 +7595,35 @@
         <v>3.6</v>
       </c>
       <c r="G123" t="n">
+        <v>47</v>
+      </c>
+      <c r="H123" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I123" t="n">
         <v>35</v>
       </c>
-      <c r="H123" t="n">
+      <c r="J123" t="n">
         <v>14</v>
       </c>
-      <c r="I123" t="n">
+      <c r="K123" t="n">
         <v>24</v>
       </c>
-      <c r="J123" t="n">
+      <c r="L123" t="n">
         <v>2</v>
       </c>
-      <c r="K123" t="n">
+      <c r="M123" t="n">
         <v>8.09</v>
       </c>
-      <c r="L123" t="n">
+      <c r="N123" t="n">
         <v>194</v>
       </c>
-      <c r="M123" t="n">
+      <c r="O123" t="n">
         <v>42</v>
       </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6911,29 +7653,35 @@
         <v>3.6</v>
       </c>
       <c r="G124" t="n">
+        <v>29</v>
+      </c>
+      <c r="H124" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I124" t="n">
         <v>28</v>
       </c>
-      <c r="H124" t="n">
+      <c r="J124" t="n">
         <v>14</v>
       </c>
-      <c r="I124" t="n">
+      <c r="K124" t="n">
         <v>12</v>
       </c>
-      <c r="J124" t="n">
+      <c r="L124" t="n">
         <v>2</v>
       </c>
-      <c r="K124" t="n">
+      <c r="M124" t="n">
         <v>16.6</v>
       </c>
-      <c r="L124" t="n">
+      <c r="N124" t="n">
         <v>199</v>
       </c>
-      <c r="M124" t="n">
+      <c r="O124" t="n">
         <v>31</v>
       </c>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6963,29 +7711,35 @@
         <v>3.6</v>
       </c>
       <c r="G125" t="n">
+        <v>71</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I125" t="n">
         <v>9</v>
       </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
         <v>12</v>
       </c>
-      <c r="J125" t="n">
+      <c r="L125" t="n">
         <v>2</v>
       </c>
-      <c r="K125" t="n">
+      <c r="M125" t="n">
         <v>16.23</v>
       </c>
-      <c r="L125" t="n">
+      <c r="N125" t="n">
         <v>195</v>
       </c>
-      <c r="M125" t="n">
+      <c r="O125" t="n">
         <v>40</v>
       </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7015,29 +7769,35 @@
         <v>3.6</v>
       </c>
       <c r="G126" t="n">
+        <v>34</v>
+      </c>
+      <c r="H126" t="n">
+        <v>5</v>
+      </c>
+      <c r="I126" t="n">
         <v>38</v>
       </c>
-      <c r="H126" t="n">
+      <c r="J126" t="n">
         <v>28</v>
       </c>
-      <c r="I126" t="n">
+      <c r="K126" t="n">
         <v>12</v>
       </c>
-      <c r="J126" t="n">
+      <c r="L126" t="n">
         <v>1</v>
       </c>
-      <c r="K126" t="n">
+      <c r="M126" t="n">
         <v>5.08</v>
       </c>
-      <c r="L126" t="n">
+      <c r="N126" t="n">
         <v>61</v>
       </c>
-      <c r="M126" t="n">
+      <c r="O126" t="n">
         <v>43</v>
       </c>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7067,29 +7827,35 @@
         <v>3.6</v>
       </c>
       <c r="G127" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I127" t="n">
         <v>5</v>
       </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
         <v>6</v>
       </c>
-      <c r="J127" t="n">
+      <c r="L127" t="n">
         <v>1</v>
       </c>
-      <c r="K127" t="n">
+      <c r="M127" t="n">
         <v>30</v>
       </c>
-      <c r="L127" t="n">
+      <c r="N127" t="n">
         <v>180</v>
       </c>
-      <c r="M127" t="n">
+      <c r="O127" t="n">
         <v>37</v>
       </c>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7119,29 +7885,35 @@
         <v>3.7</v>
       </c>
       <c r="G128" t="n">
+        <v>14</v>
+      </c>
+      <c r="H128" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="I128" t="n">
         <v>728</v>
       </c>
-      <c r="H128" t="n">
+      <c r="J128" t="n">
         <v>577</v>
       </c>
-      <c r="I128" t="n">
+      <c r="K128" t="n">
         <v>120</v>
       </c>
-      <c r="J128" t="n">
+      <c r="L128" t="n">
         <v>1</v>
       </c>
-      <c r="K128" t="n">
+      <c r="M128" t="n">
         <v>0.6</v>
       </c>
-      <c r="L128" t="n">
+      <c r="N128" t="n">
         <v>72</v>
       </c>
-      <c r="M128" t="n">
+      <c r="O128" t="n">
         <v>60</v>
       </c>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7171,29 +7943,35 @@
         <v>3.7</v>
       </c>
       <c r="G129" t="n">
+        <v>31</v>
+      </c>
+      <c r="H129" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I129" t="n">
         <v>77</v>
       </c>
-      <c r="H129" t="n">
+      <c r="J129" t="n">
         <v>62</v>
       </c>
-      <c r="I129" t="n">
+      <c r="K129" t="n">
         <v>12</v>
       </c>
-      <c r="J129" t="n">
+      <c r="L129" t="n">
         <v>1</v>
       </c>
-      <c r="K129" t="n">
+      <c r="M129" t="n">
         <v>11.96</v>
       </c>
-      <c r="L129" t="n">
+      <c r="N129" t="n">
         <v>143</v>
       </c>
-      <c r="M129" t="n">
+      <c r="O129" t="n">
         <v>37</v>
       </c>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7223,29 +8001,35 @@
         <v>3.8</v>
       </c>
       <c r="G130" t="n">
+        <v>18</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
         <v>136</v>
       </c>
-      <c r="H130" t="n">
+      <c r="J130" t="n">
         <v>108</v>
       </c>
-      <c r="I130" t="n">
+      <c r="K130" t="n">
         <v>24</v>
       </c>
-      <c r="J130" t="n">
+      <c r="L130" t="n">
         <v>1</v>
       </c>
-      <c r="K130" t="n">
+      <c r="M130" t="n">
         <v>0.39</v>
       </c>
-      <c r="L130" t="n">
+      <c r="N130" t="n">
         <v>9</v>
       </c>
-      <c r="M130" t="n">
+      <c r="O130" t="n">
         <v>91</v>
       </c>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7275,29 +8059,35 @@
         <v>3.8</v>
       </c>
       <c r="G131" t="n">
+        <v>9</v>
+      </c>
+      <c r="H131" t="n">
+        <v>413.8</v>
+      </c>
+      <c r="I131" t="n">
         <v>687</v>
       </c>
-      <c r="H131" t="n">
+      <c r="J131" t="n">
         <v>592</v>
       </c>
-      <c r="I131" t="n">
+      <c r="K131" t="n">
         <v>96</v>
       </c>
-      <c r="J131" t="n">
+      <c r="L131" t="n">
         <v>2</v>
       </c>
-      <c r="K131" t="n">
+      <c r="M131" t="n">
         <v>1.19</v>
       </c>
-      <c r="L131" t="n">
+      <c r="N131" t="n">
         <v>114</v>
       </c>
-      <c r="M131" t="n">
+      <c r="O131" t="n">
         <v>48</v>
       </c>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7327,33 +8117,39 @@
         <v>3.8</v>
       </c>
       <c r="G132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I132" t="n">
         <v>23</v>
       </c>
-      <c r="H132" t="n">
+      <c r="J132" t="n">
         <v>12</v>
       </c>
-      <c r="I132" t="n">
+      <c r="K132" t="n">
         <v>12</v>
       </c>
-      <c r="J132" t="n">
+      <c r="L132" t="n">
         <v>2</v>
       </c>
-      <c r="K132" t="n">
+      <c r="M132" t="n">
         <v>15.23</v>
       </c>
-      <c r="L132" t="n">
+      <c r="N132" t="n">
         <v>183</v>
       </c>
-      <c r="M132" t="n">
+      <c r="O132" t="n">
         <v>24</v>
       </c>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr">
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec)</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7383,29 +8179,35 @@
         <v>3.8</v>
       </c>
       <c r="G133" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H133" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I133" t="n">
         <v>13</v>
       </c>
-      <c r="H133" t="n">
+      <c r="J133" t="n">
         <v>4</v>
       </c>
-      <c r="I133" t="n">
+      <c r="K133" t="n">
         <v>12</v>
       </c>
-      <c r="J133" t="n">
+      <c r="L133" t="n">
         <v>2</v>
       </c>
-      <c r="K133" t="n">
+      <c r="M133" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="L133" t="n">
+      <c r="N133" t="n">
         <v>97</v>
       </c>
-      <c r="M133" t="n">
+      <c r="O133" t="n">
         <v>46</v>
       </c>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7435,29 +8237,35 @@
         <v>3.8</v>
       </c>
       <c r="G134" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="n">
         <v>5</v>
       </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
         <v>6</v>
       </c>
-      <c r="J134" t="n">
+      <c r="L134" t="n">
         <v>1</v>
       </c>
-      <c r="K134" t="n">
+      <c r="M134" t="n">
         <v>30.8</v>
       </c>
-      <c r="L134" t="n">
+      <c r="N134" t="n">
         <v>185</v>
       </c>
-      <c r="M134" t="n">
+      <c r="O134" t="n">
         <v>36</v>
       </c>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7490,26 +8298,32 @@
         <v>8</v>
       </c>
       <c r="H135" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I135" t="n">
+        <v>8</v>
+      </c>
+      <c r="J135" t="n">
         <v>4</v>
       </c>
-      <c r="I135" t="n">
+      <c r="K135" t="n">
         <v>6</v>
       </c>
-      <c r="J135" t="n">
+      <c r="L135" t="n">
         <v>1</v>
       </c>
-      <c r="K135" t="n">
+      <c r="M135" t="n">
         <v>9</v>
       </c>
-      <c r="L135" t="n">
+      <c r="N135" t="n">
         <v>54</v>
       </c>
-      <c r="M135" t="n">
+      <c r="O135" t="n">
         <v>44</v>
       </c>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7539,29 +8353,35 @@
         <v>3.9</v>
       </c>
       <c r="G136" t="n">
+        <v>44</v>
+      </c>
+      <c r="H136" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I136" t="n">
         <v>35</v>
       </c>
-      <c r="H136" t="n">
+      <c r="J136" t="n">
         <v>22</v>
       </c>
-      <c r="I136" t="n">
+      <c r="K136" t="n">
         <v>12</v>
       </c>
-      <c r="J136" t="n">
+      <c r="L136" t="n">
         <v>2</v>
       </c>
-      <c r="K136" t="n">
+      <c r="M136" t="n">
         <v>44.98</v>
       </c>
-      <c r="L136" t="n">
+      <c r="N136" t="n">
         <v>540</v>
       </c>
-      <c r="M136" t="n">
+      <c r="O136" t="n">
         <v>21</v>
       </c>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7591,29 +8411,35 @@
         <v>3.9</v>
       </c>
       <c r="G137" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H137" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I137" t="n">
         <v>41</v>
       </c>
-      <c r="H137" t="n">
+      <c r="J137" t="n">
         <v>32</v>
       </c>
-      <c r="I137" t="n">
+      <c r="K137" t="n">
         <v>12</v>
       </c>
-      <c r="J137" t="n">
+      <c r="L137" t="n">
         <v>2</v>
       </c>
-      <c r="K137" t="n">
+      <c r="M137" t="n">
         <v>15.35</v>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>184</v>
       </c>
-      <c r="M137" t="n">
+      <c r="O137" t="n">
         <v>36</v>
       </c>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7643,29 +8469,35 @@
         <v>3.9</v>
       </c>
       <c r="G138" t="n">
+        <v>12</v>
+      </c>
+      <c r="H138" t="n">
+        <v>13</v>
+      </c>
+      <c r="I138" t="n">
         <v>34</v>
       </c>
-      <c r="H138" t="n">
+      <c r="J138" t="n">
         <v>20</v>
       </c>
-      <c r="I138" t="n">
+      <c r="K138" t="n">
         <v>12</v>
       </c>
-      <c r="J138" t="n">
+      <c r="L138" t="n">
         <v>1</v>
       </c>
-      <c r="K138" t="n">
+      <c r="M138" t="n">
         <v>8.44</v>
       </c>
-      <c r="L138" t="n">
+      <c r="N138" t="n">
         <v>101</v>
       </c>
-      <c r="M138" t="n">
+      <c r="O138" t="n">
         <v>50</v>
       </c>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7695,33 +8527,39 @@
         <v>3.9</v>
       </c>
       <c r="G139" t="n">
+        <v>13</v>
+      </c>
+      <c r="H139" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I139" t="n">
         <v>16</v>
       </c>
-      <c r="H139" t="n">
+      <c r="J139" t="n">
         <v>9</v>
       </c>
-      <c r="I139" t="n">
+      <c r="K139" t="n">
         <v>12</v>
       </c>
-      <c r="J139" t="n">
+      <c r="L139" t="n">
         <v>1</v>
       </c>
-      <c r="K139" t="n">
+      <c r="M139" t="n">
         <v>14.37</v>
       </c>
-      <c r="L139" t="n">
+      <c r="N139" t="n">
         <v>172</v>
       </c>
-      <c r="M139" t="n">
+      <c r="O139" t="n">
         <v>40</v>
       </c>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr">
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
         <is>
           <t>In buy-month (Feb, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7751,29 +8589,35 @@
         <v>3.9</v>
       </c>
       <c r="G140" t="n">
+        <v>-45</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
         <v>5</v>
       </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
         <v>6</v>
       </c>
-      <c r="J140" t="n">
+      <c r="L140" t="n">
         <v>1</v>
       </c>
-      <c r="K140" t="n">
+      <c r="M140" t="n">
         <v>8.24</v>
       </c>
-      <c r="L140" t="n">
+      <c r="N140" t="n">
         <v>49</v>
       </c>
-      <c r="M140" t="n">
+      <c r="O140" t="n">
         <v>37</v>
       </c>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7786,7 +8630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7822,55 +8666,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -7899,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -7908,24 +8762,30 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>11.18</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>11</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>36</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: Mar, Jun, Aug, Nov, Dec)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -7959,29 +8819,35 @@
         <v>0.7</v>
       </c>
       <c r="G3" t="n">
+        <v>199</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>183</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>15</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>168</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>28</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>55.66</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>9351</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>99</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Margin over 95% - check retail; Large buy ($9,351) - confirm</t>
         </is>
@@ -8015,29 +8881,35 @@
         <v>1.2</v>
       </c>
       <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>183.05</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>1098</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>-281</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -8071,7 +8943,7 @@
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -8080,20 +8952,26 @@
         <v>12</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>100</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -8127,29 +9005,35 @@
         <v>1.5</v>
       </c>
       <c r="G6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I6" t="n">
         <v>325</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>324</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>27</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>15.31</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>4961</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>36</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>Large buy ($4,961) - confirm</t>
         </is>
@@ -8183,33 +9067,39 @@
         <v>1.9</v>
       </c>
       <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I7" t="n">
         <v>56</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>54</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>9</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>23.25</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>1255</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>34</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: Mar, Jun, Sep, Dec)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -8243,29 +9133,35 @@
         <v>2.7</v>
       </c>
       <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="I8" t="n">
         <v>96</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>21</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>72</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>112.79</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>8121</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>-169</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost; Large buy ($8,121) - confirm</t>
         </is>
@@ -8282,7 +9178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8318,45 +9214,55 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
@@ -8390,27 +9296,33 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>63.38</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>380</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>19</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8440,27 +9352,33 @@
         <v>0.4</v>
       </c>
       <c r="G3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>119</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>108</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>9</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>21.25</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>2295</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>52</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8490,27 +9408,33 @@
         <v>2.6</v>
       </c>
       <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
         <v>37</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>24</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>15.04</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>361</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>32</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8540,27 +9464,33 @@
         <v>3.6</v>
       </c>
       <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I5" t="n">
         <v>31</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>21</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>15</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>315</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>32</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8585,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -8594,18 +9524,24 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>229</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>229</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>18</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8635,27 +9571,33 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I7" t="n">
         <v>73</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>16</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>60</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>10</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>36.64</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>2199</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>19</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8685,27 +9627,33 @@
         <v>2.6</v>
       </c>
       <c r="G8" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>7</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>12</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>6.66</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>80</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>52</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8735,27 +9683,33 @@
         <v>1.8</v>
       </c>
       <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" t="n">
         <v>5</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>14.5</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>87</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>15</v>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8780,27 +9734,33 @@
         <v>1.3</v>
       </c>
       <c r="G10" t="n">
+        <v>-55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>28</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>8</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>20</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>20</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>6.52</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>130</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>63</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8830,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>-14</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -8839,18 +9799,24 @@
         <v>6</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>13</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>78</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>-0</v>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8880,27 +9846,33 @@
         <v>1.7</v>
       </c>
       <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I12" t="n">
         <v>20</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>18</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>7.5</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>135</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>40</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8925,7 +9897,7 @@
         <v>-1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -8934,18 +9906,24 @@
         <v>5</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
         <v>80.83</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>404</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>27</v>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8975,27 +9953,33 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>37</v>
+      </c>
+      <c r="I14" t="n">
         <v>59</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>27</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>30</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>14.99</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>450</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>35</v>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9020,7 +10004,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -9029,18 +10013,24 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
         <v>13.21</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>26</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>34</v>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9070,27 +10060,33 @@
         <v>2.8</v>
       </c>
       <c r="G16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>121</v>
+      </c>
+      <c r="I16" t="n">
         <v>155</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>49</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>96</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>3.24</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>311</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>64</v>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9120,27 +10116,33 @@
         <v>3.7</v>
       </c>
       <c r="G17" t="n">
+        <v>146</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>14</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>6</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>14.58</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>87</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>21</v>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9170,27 +10172,33 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I18" t="n">
         <v>124</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>11</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>108</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>9</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>9.74</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>1052</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>35</v>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9220,27 +10228,33 @@
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>36</v>
+      </c>
+      <c r="I19" t="n">
         <v>81</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>58</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>24</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>2.42</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>58</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>51</v>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9270,27 +10284,33 @@
         <v>2.7</v>
       </c>
       <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I20" t="n">
         <v>80</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>32</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>48</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>27.52</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>1321</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>22</v>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9320,27 +10340,33 @@
         <v>2.2</v>
       </c>
       <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>400.2</v>
+      </c>
+      <c r="I21" t="n">
         <v>867</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>864</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>144</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>27.32</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>23600</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>20</v>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9370,27 +10396,33 @@
         <v>1.4</v>
       </c>
       <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>86</v>
+      </c>
+      <c r="I22" t="n">
         <v>257</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>252</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>21</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>8.25</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>2079</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>45</v>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9420,27 +10452,33 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>152</v>
+      </c>
+      <c r="I23" t="n">
         <v>434</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>432</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>36</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>5.54</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>2395</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>72</v>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9470,27 +10508,33 @@
         <v>2.3</v>
       </c>
       <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="I24" t="n">
         <v>440</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>44</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>396</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>33</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>18.17</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>7194</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>27</v>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9520,27 +10564,33 @@
         <v>3.6</v>
       </c>
       <c r="G25" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I25" t="n">
         <v>51</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>34</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>18</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>3</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>48.77</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>878</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>14</v>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9553,7 +10603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9589,50 +10639,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
@@ -9666,28 +10726,34 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="n">
         <v>74</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>66</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>11</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>14.78</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>975</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>36</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Wait for buy-month (Mar, Jun, Aug, Oct, Dec)</t>
         </is>
@@ -9721,28 +10787,34 @@
         <v>3.8</v>
       </c>
       <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I3" t="n">
         <v>19</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>18</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>17.67</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>318</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>35</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Wait for buy-month (Mar, Jun, Aug, Oct, Dec)</t>
         </is>
@@ -9776,28 +10848,34 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>53</v>
+      </c>
+      <c r="I4" t="n">
         <v>106</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>102</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>17</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>15.6</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>1591</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>35</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Wait for buy-month (Feb, May, Sep, Dec)</t>
         </is>
@@ -9831,28 +10909,34 @@
         <v>2.3</v>
       </c>
       <c r="G5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="I5" t="n">
         <v>133</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>29</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>102</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>17</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>17.39</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>1774</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>24</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Wait for buy-month (Jan, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
@@ -9886,28 +10970,34 @@
         <v>3.4</v>
       </c>
       <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I6" t="n">
         <v>90</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>51</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>36</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>14.74</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>531</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>39</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>Wait for buy-month (Feb, Apr, May, Aug, Oct, Nov)</t>
         </is>
@@ -9941,28 +11031,34 @@
         <v>3.2</v>
       </c>
       <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I7" t="n">
         <v>40</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>24</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>18</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>26.4</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>475</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>31</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Wait for buy-month (Feb, Apr, May, Aug, Oct, Nov)</t>
         </is>
@@ -9996,28 +11092,34 @@
         <v>2.4</v>
       </c>
       <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I8" t="n">
         <v>109</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>56</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>48</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>10.18</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>489</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>43</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
@@ -10051,28 +11153,34 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="I9" t="n">
         <v>170</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>168</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>14</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>6.57</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>1104</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>49</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>Wait for buy-month (Feb, May, Aug, Nov, Dec)</t>
         </is>
@@ -10106,28 +11214,34 @@
         <v>2.7</v>
       </c>
       <c r="G10" t="n">
+        <v>43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I10" t="n">
         <v>40</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>13</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>24</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>26.25</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>630</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>31</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Wait for buy-month (Mar, Jun, Sep, Dec)</t>
         </is>

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S210"/>
+  <dimension ref="A1:S211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10136,12 +10136,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>New Amsterdam Watermelon 1.75L</t>
+          <t>New Amsterdam Vodka 200ml</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>085000030943</t>
+          <t>085000019474</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10155,323 +10155,319 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="F162" t="n">
         <v>6.4</v>
       </c>
       <c r="G162" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H162" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K162" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="L162" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>15.5</v>
+        <v>3.99</v>
       </c>
       <c r="N162" t="n">
-        <v>1116</v>
+        <v>96</v>
       </c>
       <c r="O162" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($1,116 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Bulleit 95 Rye Whiskey 1.75L</t>
+          <t>New Amsterdam Watermelon 1.75L</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>082000766070</t>
+          <t>085000030943</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F163" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G163" t="n">
-        <v>-11</v>
+        <v>20</v>
       </c>
       <c r="H163" t="n">
-        <v>10.2</v>
+        <v>1.8</v>
       </c>
       <c r="I163" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="L163" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M163" t="n">
-        <v>38.11</v>
+        <v>15.5</v>
       </c>
       <c r="N163" t="n">
-        <v>686</v>
+        <v>1116</v>
       </c>
       <c r="O163" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($686 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,116 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Patron Silver Tequila 375ml</t>
+          <t>Bulleit 95 Rye Whiskey 1.75L</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>721733000944</t>
+          <t>082000766070</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F164" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="H164" t="n">
-        <v>17.2</v>
+        <v>10.2</v>
       </c>
       <c r="I164" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J164" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K164" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M164" t="n">
-        <v>30.64</v>
+        <v>38.11</v>
       </c>
       <c r="N164" t="n">
-        <v>735</v>
+        <v>686</v>
       </c>
       <c r="O164" t="n">
-        <v>-0</v>
+        <v>28</v>
       </c>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($735 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($686 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Absolut Citron Vodka 1.75L</t>
+          <t>Patron Silver Tequila 375ml</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>835229001602</t>
+          <t>721733000944</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="F165" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="G165" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H165" t="n">
-        <v>5.2</v>
+        <v>17.2</v>
       </c>
       <c r="I165" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K165" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L165" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M165" t="n">
-        <v>30.23</v>
+        <v>30.64</v>
       </c>
       <c r="N165" t="n">
-        <v>907</v>
+        <v>735</v>
       </c>
       <c r="O165" t="n">
-        <v>14</v>
+        <v>-0</v>
       </c>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($907 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($735 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Crown Royal Regal Apple 1.75L</t>
+          <t>Absolut Citron Vodka 1.75L</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>082000771593</t>
+          <t>835229001602</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="F166" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="G166" t="n">
-        <v>18</v>
+        <v>-8</v>
       </c>
       <c r="H166" t="n">
-        <v>12.2</v>
+        <v>5.2</v>
       </c>
       <c r="I166" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J166" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M166" t="n">
-        <v>36.99</v>
+        <v>30.23</v>
       </c>
       <c r="N166" t="n">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="O166" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($888 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($907 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Bulleit Bourbon Liter</t>
+          <t>Crown Royal Regal Apple 1.75L</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>087000005549</t>
+          <t>082000771593</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10481,41 +10477,41 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="F167" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H167" t="n">
-        <v>16.2</v>
+        <v>12.2</v>
       </c>
       <c r="I167" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J167" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K167" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M167" t="n">
-        <v>23.33</v>
+        <v>36.99</v>
       </c>
       <c r="N167" t="n">
-        <v>280</v>
+        <v>888</v>
       </c>
       <c r="O167" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr">
@@ -10525,24 +10521,24 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($280 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($888 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Bailey's Irish Cream 1.75L</t>
+          <t>Bulleit Bourbon Liter</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>086767210029</t>
+          <t>087000005549</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10551,34 +10547,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G168" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="I168" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J168" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K168" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L168" t="n">
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>32.53</v>
+        <v>23.33</v>
       </c>
       <c r="N168" t="n">
-        <v>195</v>
+        <v>280</v>
       </c>
       <c r="O168" t="n">
         <v>39</v>
@@ -10591,24 +10587,24 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($195 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($280 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Crown Royal Peach 1.75L</t>
+          <t>Bailey's Irish Cream 1.75L</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>082000795360</t>
+          <t>086767210029</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10617,19 +10613,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="F169" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="G169" t="n">
-        <v>-5</v>
+        <v>-18</v>
       </c>
       <c r="H169" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I169" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J169" t="n">
         <v>4</v>
@@ -10641,13 +10637,13 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>36.88</v>
+        <v>32.53</v>
       </c>
       <c r="N169" t="n">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="O169" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr">
@@ -10657,90 +10653,90 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($221 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($195 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Absolut Vodka Liter</t>
+          <t>Crown Royal Peach 1.75L</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>835229000407</t>
+          <t>082000795360</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>281</v>
+        <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G170" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" t="n">
         <v>10</v>
       </c>
-      <c r="H170" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="I170" t="n">
-        <v>32</v>
-      </c>
       <c r="J170" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K170" t="n">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="L170" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>19.08</v>
+        <v>36.88</v>
       </c>
       <c r="N170" t="n">
-        <v>2977</v>
+        <v>221</v>
       </c>
       <c r="O170" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($2,977 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($221 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Larceny Bourbon 1.75L</t>
+          <t>Absolut Vodka Liter</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>096749031535</t>
+          <t>835229000407</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10749,85 +10745,85 @@
         </is>
       </c>
       <c r="E171" t="n">
+        <v>281</v>
+      </c>
+      <c r="F171" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G171" t="n">
         <v>10</v>
       </c>
-      <c r="F171" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G171" t="n">
-        <v>114</v>
-      </c>
       <c r="H171" t="n">
-        <v>1.2</v>
+        <v>21.8</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K171" t="n">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="L171" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M171" t="n">
-        <v>38.09</v>
+        <v>19.08</v>
       </c>
       <c r="N171" t="n">
-        <v>229</v>
+        <v>2977</v>
       </c>
       <c r="O171" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($229 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($2,977 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>New Amsterdam London Dry Gin 1.75L</t>
+          <t>Larceny Bourbon 1.75L</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>085000028308</t>
+          <t>096749031535</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F172" t="n">
         <v>8.6</v>
       </c>
       <c r="G172" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -10839,35 +10835,35 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>19.47</v>
+        <v>38.09</v>
       </c>
       <c r="N172" t="n">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="O172" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($117 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($229 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Seagrams Lime Gin 1.75L</t>
+          <t>New Amsterdam London Dry Gin 1.75L</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>080432401644</t>
+          <t>085000028308</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10877,195 +10873,195 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F173" t="n">
         <v>8.6</v>
       </c>
       <c r="G173" t="n">
-        <v>-29</v>
+        <v>200</v>
       </c>
       <c r="H173" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="I173" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>31.28</v>
+        <v>19.47</v>
       </c>
       <c r="N173" t="n">
-        <v>563</v>
+        <v>117</v>
       </c>
       <c r="O173" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($563 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($117 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Twisted Shotz Party Pack Red</t>
+          <t>Seagrams Lime Gin 1.75L</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>766427005355</t>
+          <t>080432401644</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F174" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G174" t="n">
-        <v>-42</v>
+        <v>-29</v>
       </c>
       <c r="H174" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K174" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M174" t="n">
-        <v>13.68</v>
+        <v>31.28</v>
       </c>
       <c r="N174" t="n">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="O174" t="n">
-        <v>43</v>
+        <v>-30</v>
       </c>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr">
         <is>
-          <t>In buy-month (Jun, Jul, Sep, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($82 to next deal) - confirm</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($563 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Crown Royal Canadian Liter</t>
+          <t>Twisted Shotz Party Pack Red</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>087000007246</t>
+          <t>766427005355</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Pre-Mix</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F175" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G175" t="n">
-        <v>-22</v>
+        <v>-42</v>
       </c>
       <c r="H175" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="I175" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L175" t="n">
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>26.2</v>
+        <v>13.68</v>
       </c>
       <c r="N175" t="n">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="O175" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jun, Jul, Sep, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($314 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($82 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>George Dickel No 12 750ml</t>
+          <t>Crown Royal Canadian Liter</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>088076006232</t>
+          <t>087000007246</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11075,23 +11071,23 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="F176" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G176" t="n">
-        <v>35</v>
+        <v>-22</v>
       </c>
       <c r="H176" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -11103,13 +11099,13 @@
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>18.84</v>
+        <v>26.2</v>
       </c>
       <c r="N176" t="n">
-        <v>226</v>
+        <v>314</v>
       </c>
       <c r="O176" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr">
@@ -11119,24 +11115,24 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($226 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($314 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Smirnoff Strawberry &amp; Rose Zero Sugar 750ml</t>
+          <t>George Dickel No 12 750ml</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>082000790815</t>
+          <t>088076006232</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11145,22 +11141,22 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="F177" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="G177" t="n">
-        <v>-12</v>
+        <v>35</v>
       </c>
       <c r="H177" t="n">
-        <v>9.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="I177" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
         <v>12</v>
@@ -11169,13 +11165,13 @@
         <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>8.01</v>
+        <v>18.84</v>
       </c>
       <c r="N177" t="n">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="O177" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
@@ -11185,48 +11181,48 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($226 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Bulleit 95 Rye Whiskey Liter</t>
+          <t>Smirnoff Strawberry &amp; Rose Zero Sugar 750ml</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>082000752974</t>
+          <t>082000790815</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F178" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="G178" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="H178" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I178" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J178" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K178" t="n">
         <v>12</v>
@@ -11235,13 +11231,13 @@
         <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>23.33</v>
+        <v>8.01</v>
       </c>
       <c r="N178" t="n">
-        <v>280</v>
+        <v>96</v>
       </c>
       <c r="O178" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr">
@@ -11251,19 +11247,19 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($280 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Windsor Apple 1.75L</t>
+          <t>Bulleit 95 Rye Whiskey Liter</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>084279007403</t>
+          <t>082000752974</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11277,130 +11273,130 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F179" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="G179" t="n">
-        <v>-28</v>
+        <v>-10</v>
       </c>
       <c r="H179" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="I179" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J179" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K179" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>15.31</v>
+        <v>23.33</v>
       </c>
       <c r="N179" t="n">
-        <v>92</v>
+        <v>280</v>
       </c>
       <c r="O179" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($280 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Absolut Citron Vodka Liter</t>
+          <t>Windsor Apple 1.75L</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>835229001404</t>
+          <t>084279007403</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="F180" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="G180" t="n">
-        <v>-14</v>
+        <v>-28</v>
       </c>
       <c r="H180" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="I180" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J180" t="n">
         <v>4</v>
       </c>
       <c r="K180" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L180" t="n">
         <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>19.43</v>
+        <v>15.31</v>
       </c>
       <c r="N180" t="n">
-        <v>233</v>
+        <v>92</v>
       </c>
       <c r="O180" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($233 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Larceny Bourbon 750ml</t>
+          <t>Absolut Citron Vodka Liter</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>096749031559</t>
+          <t>835229001404</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11409,22 +11405,22 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F181" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="G181" t="n">
-        <v>-35</v>
+        <v>-14</v>
       </c>
       <c r="H181" t="n">
-        <v>10.8</v>
+        <v>6.2</v>
       </c>
       <c r="I181" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K181" t="n">
         <v>12</v>
@@ -11433,35 +11429,35 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>17.42</v>
+        <v>19.43</v>
       </c>
       <c r="N181" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="O181" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~11/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($233 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>George Dickel Rye 750ml</t>
+          <t>Larceny Bourbon 750ml</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>082000759454</t>
+          <t>096749031559</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11471,26 +11467,26 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F182" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="G182" t="n">
-        <v>9</v>
+        <v>-35</v>
       </c>
       <c r="H182" t="n">
-        <v>1.5</v>
+        <v>10.8</v>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K182" t="n">
         <v>12</v>
@@ -11499,61 +11495,61 @@
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>18.78</v>
+        <v>17.42</v>
       </c>
       <c r="N182" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="O182" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($225 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~11/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Dos Amigos Tequila Reposado 750ml</t>
+          <t>George Dickel Rye 750ml</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>698450104463</t>
+          <t>082000759454</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>New France Wine Co, Inc</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="F183" t="n">
-        <v>13.1</v>
+        <v>12.3</v>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -11565,127 +11561,127 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>21.99</v>
+        <v>18.78</v>
       </c>
       <c r="N183" t="n">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="O183" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>Overstocked (13 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($225 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Teeling Small Batch 750ml</t>
+          <t>Dos Amigos Tequila Reposado 750ml</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>720815280038</t>
+          <t>698450104463</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>New France Wine Co, Inc</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="F184" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="G184" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H184" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L184" t="n">
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>22.33</v>
+        <v>21.99</v>
       </c>
       <c r="N184" t="n">
-        <v>134</v>
+        <v>264</v>
       </c>
       <c r="O184" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($134 to next deal) - confirm</t>
+          <t>Overstocked (13 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Phillips Blackberry Brandy 1.75L</t>
+          <t>Teeling Small Batch 750ml</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>087116003507</t>
+          <t>720815280038</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F185" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="G185" t="n">
-        <v>-29</v>
+        <v>15</v>
       </c>
       <c r="H185" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -11697,106 +11693,106 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>15.34</v>
+        <v>22.33</v>
       </c>
       <c r="N185" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="O185" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($134 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Absolut Ruby Red Vodka Liter</t>
+          <t>Phillips Blackberry Brandy 1.75L</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>835229001244</t>
+          <t>087116003507</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="F186" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="G186" t="n">
-        <v>47</v>
+        <v>-29</v>
       </c>
       <c r="H186" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L186" t="n">
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>19.04</v>
+        <v>15.34</v>
       </c>
       <c r="N186" t="n">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="O186" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Seagrams Extra Dry Gin Traveler</t>
+          <t>Absolut Ruby Red Vodka Liter</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>080432401248</t>
+          <t>835229001244</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11805,19 +11801,19 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="F187" t="n">
         <v>14.6</v>
       </c>
       <c r="G187" t="n">
-        <v>-6</v>
+        <v>47</v>
       </c>
       <c r="H187" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="I187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -11829,13 +11825,13 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>7.8</v>
+        <v>19.04</v>
       </c>
       <c r="N187" t="n">
-        <v>94</v>
+        <v>228</v>
       </c>
       <c r="O187" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr">
@@ -11845,24 +11841,24 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($94 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Absolut Vodka 750ml</t>
+          <t>Seagrams Extra Dry Gin Traveler</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>835229000308</t>
+          <t>080432401248</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11871,22 +11867,22 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>265</v>
+        <v>17</v>
       </c>
       <c r="F188" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="G188" t="n">
-        <v>21</v>
+        <v>-6</v>
       </c>
       <c r="H188" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="I188" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="J188" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
         <v>12</v>
@@ -11895,13 +11891,13 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>14.71</v>
+        <v>7.8</v>
       </c>
       <c r="N188" t="n">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="O188" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr">
@@ -11911,24 +11907,24 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($177 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($94 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>818 Tequila Blanco 750ml</t>
+          <t>Absolut Vodka 750ml</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>195893687015</t>
+          <t>835229000308</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11937,130 +11933,130 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>87</v>
+        <v>265</v>
       </c>
       <c r="F189" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H189" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K189" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L189" t="n">
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>18.98</v>
+        <v>14.71</v>
       </c>
       <c r="N189" t="n">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="O189" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr">
         <is>
-          <t>In buy-month (Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($114 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($177 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>New Amsterdam Tangerine 1.75L</t>
+          <t>818 Tequila Blanco 750ml</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>085000034835</t>
+          <t>195893687015</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="F190" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="G190" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>15.21</v>
+        <v>18.98</v>
       </c>
       <c r="N190" t="n">
-        <v>274</v>
+        <v>114</v>
       </c>
       <c r="O190" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
+          <t>In buy-month (Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($274 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($114 to next deal) - confirm; Seasonal - last year ~10/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Buchanans 12 Yr Scotch 750ml</t>
+          <t>New Amsterdam Tangerine 1.75L</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>088110955328</t>
+          <t>085000034835</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12069,34 +12065,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="F191" t="n">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="G191" t="n">
-        <v>38</v>
+        <v>-50</v>
       </c>
       <c r="H191" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M191" t="n">
-        <v>26.77</v>
+        <v>15.21</v>
       </c>
       <c r="N191" t="n">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="O191" t="n">
         <v>35</v>
@@ -12104,47 +12100,47 @@
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jun, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($274 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Patron Citronge 750ml</t>
+          <t>Buchanans 12 Yr Scotch 750ml</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>721733000043</t>
+          <t>088110955328</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F192" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="G192" t="n">
-        <v>-20</v>
+        <v>38</v>
       </c>
       <c r="H192" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="I192" t="n">
         <v>2</v>
@@ -12159,58 +12155,58 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>14.37</v>
+        <v>26.77</v>
       </c>
       <c r="N192" t="n">
-        <v>172</v>
+        <v>321</v>
       </c>
       <c r="O192" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jun, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($172 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Phillips Peach Schnapps Liter</t>
+          <t>Patron Citronge 750ml</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>087116018310</t>
+          <t>721733000043</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F193" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="G193" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="H193" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="I193" t="n">
         <v>2</v>
@@ -12225,172 +12221,172 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>8.949999999999999</v>
+        <v>14.37</v>
       </c>
       <c r="N193" t="n">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="O193" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($107 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($172 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Chopin Vodka 750ml</t>
+          <t>Phillips Peach Schnapps Liter</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>852935001153</t>
+          <t>087116018310</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F194" t="n">
-        <v>16.1</v>
+        <v>15.7</v>
       </c>
       <c r="G194" t="n">
-        <v>-43</v>
+        <v>-25</v>
       </c>
       <c r="H194" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>19.13</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N194" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O194" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($107 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Phillips Peppermint 80pf Liter</t>
+          <t>Chopin Vodka 750ml</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>087116048645</t>
+          <t>852935001153</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F195" t="n">
-        <v>17.4</v>
+        <v>16.1</v>
       </c>
       <c r="G195" t="n">
-        <v>56</v>
+        <v>-43</v>
       </c>
       <c r="H195" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="I195" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L195" t="n">
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>9.56</v>
+        <v>19.13</v>
       </c>
       <c r="N195" t="n">
         <v>115</v>
       </c>
       <c r="O195" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Phillips Blackberry Brandy Liter</t>
+          <t>Phillips Peppermint 80pf Liter</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>087116048188</t>
+          <t>087116048645</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12399,22 +12395,22 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F196" t="n">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="G196" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H196" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="I196" t="n">
+        <v>7</v>
+      </c>
+      <c r="J196" t="n">
         <v>5</v>
-      </c>
-      <c r="J196" t="n">
-        <v>0</v>
       </c>
       <c r="K196" t="n">
         <v>12</v>
@@ -12423,13 +12419,13 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>10.4</v>
+        <v>9.56</v>
       </c>
       <c r="N196" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O196" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
@@ -12439,45 +12435,45 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($125 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Absolut Mandrin Vodka Liter</t>
+          <t>Phillips Blackberry Brandy Liter</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>835229002401</t>
+          <t>087116048188</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F197" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="G197" t="n">
-        <v>-16</v>
+        <v>61</v>
       </c>
       <c r="H197" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -12489,58 +12485,58 @@
         <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>18.49</v>
+        <v>10.4</v>
       </c>
       <c r="N197" t="n">
-        <v>222</v>
+        <v>125</v>
       </c>
       <c r="O197" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($125 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Phillips Amaretto Liter</t>
+          <t>Absolut Mandrin Vodka Liter</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>087116048249</t>
+          <t>835229002401</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="F198" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="G198" t="n">
         <v>-16</v>
       </c>
       <c r="H198" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="I198" t="n">
         <v>1</v>
@@ -12555,58 +12551,58 @@
         <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>9.140000000000001</v>
+        <v>18.49</v>
       </c>
       <c r="N198" t="n">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="O198" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($110 to next deal) - confirm; Seasonal - last year ~3/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Tanqueray No. Ten Gin 750ml</t>
+          <t>Phillips Amaretto Liter</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>088110158606</t>
+          <t>087116048249</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F199" t="n">
-        <v>20.6</v>
+        <v>19.6</v>
       </c>
       <c r="G199" t="n">
-        <v>-38</v>
+        <v>-16</v>
       </c>
       <c r="H199" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I199" t="n">
         <v>1</v>
@@ -12621,79 +12617,79 @@
         <v>1</v>
       </c>
       <c r="M199" t="n">
-        <v>21.25</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N199" t="n">
-        <v>255</v>
+        <v>110</v>
       </c>
       <c r="O199" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($255 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($110 to next deal) - confirm; Seasonal - last year ~3/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Crown Royal Vanilla 1.75L</t>
+          <t>Tanqueray No. Ten Gin 750ml</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>082000776611</t>
+          <t>088110158606</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F200" t="n">
-        <v>21.4</v>
+        <v>20.6</v>
       </c>
       <c r="G200" t="n">
-        <v>-16</v>
+        <v>-38</v>
       </c>
       <c r="H200" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="I200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="n">
-        <v>36.97</v>
+        <v>21.25</v>
       </c>
       <c r="N200" t="n">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="O200" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr">
@@ -12703,24 +12699,24 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($255 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Phillips Rootbeer Schnapps Liter</t>
+          <t>Crown Royal Vanilla 1.75L</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>087116034617</t>
+          <t>082000776611</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12729,59 +12725,59 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F201" t="n">
         <v>21.4</v>
       </c>
       <c r="G201" t="n">
-        <v>50</v>
+        <v>-16</v>
       </c>
       <c r="H201" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L201" t="n">
         <v>1</v>
       </c>
       <c r="M201" t="n">
-        <v>9.07</v>
+        <v>36.97</v>
       </c>
       <c r="N201" t="n">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="O201" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Phillips Peppermint 60pf Traveler</t>
+          <t>Phillips Rootbeer Schnapps Liter</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>087116018693</t>
+          <t>087116034617</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12795,19 +12791,19 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F202" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="G202" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H202" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I202" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -12819,13 +12815,13 @@
         <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>7.01</v>
+        <v>9.07</v>
       </c>
       <c r="N202" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="O202" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
@@ -12835,45 +12831,45 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Captain Morgan 100 Proof Liter</t>
+          <t>Phillips Peppermint 60pf Traveler</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>082000741992</t>
+          <t>087116018693</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F203" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="G203" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H203" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -12885,61 +12881,61 @@
         <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>19.27</v>
+        <v>7.01</v>
       </c>
       <c r="N203" t="n">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="O203" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Absolut Pears Vodka Liter</t>
+          <t>Captain Morgan 100 Proof Liter</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>835229001343</t>
+          <t>082000741992</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="F204" t="n">
-        <v>26.2</v>
+        <v>23.6</v>
       </c>
       <c r="G204" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H204" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="I204" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -12951,35 +12947,35 @@
         <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>19.08</v>
+        <v>19.27</v>
       </c>
       <c r="N204" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O204" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($229 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ciroc Apple 750ml</t>
+          <t>Absolut Pears Vodka Liter</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>088076180451</t>
+          <t>835229001343</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12989,23 +12985,23 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="F205" t="n">
-        <v>29.3</v>
+        <v>26.2</v>
       </c>
       <c r="G205" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H205" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -13017,61 +13013,61 @@
         <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>21.53</v>
+        <v>19.08</v>
       </c>
       <c r="N205" t="n">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="O205" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($229 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Crown Royal Regal Apple Liter</t>
+          <t>Ciroc Apple 750ml</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>082000771586</t>
+          <t>088076180451</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>244</v>
+        <v>41</v>
       </c>
       <c r="F206" t="n">
-        <v>30.8</v>
+        <v>29.3</v>
       </c>
       <c r="G206" t="n">
-        <v>-18</v>
+        <v>29</v>
       </c>
       <c r="H206" t="n">
-        <v>8.800000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I206" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -13083,13 +13079,13 @@
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>26.66</v>
+        <v>21.53</v>
       </c>
       <c r="N206" t="n">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="O206" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr">
@@ -13099,45 +13095,45 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($320 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ciroc Peach Vodka 750ml</t>
+          <t>Crown Royal Regal Apple Liter</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>088076177406</t>
+          <t>082000771586</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="F207" t="n">
-        <v>34.3</v>
+        <v>30.8</v>
       </c>
       <c r="G207" t="n">
-        <v>-33</v>
+        <v>-18</v>
       </c>
       <c r="H207" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -13149,13 +13145,13 @@
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>21.53</v>
+        <v>26.66</v>
       </c>
       <c r="N207" t="n">
-        <v>258</v>
+        <v>320</v>
       </c>
       <c r="O207" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
@@ -13165,19 +13161,19 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($320 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ciroc Vodka 750ml</t>
+          <t>Ciroc Peach Vodka 750ml</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>088076161863</t>
+          <t>088076177406</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13191,19 +13187,19 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="F208" t="n">
-        <v>38.2</v>
+        <v>34.3</v>
       </c>
       <c r="G208" t="n">
-        <v>32</v>
+        <v>-33</v>
       </c>
       <c r="H208" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -13215,13 +13211,13 @@
         <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>22.05</v>
+        <v>21.53</v>
       </c>
       <c r="N208" t="n">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="O208" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr">
@@ -13231,42 +13227,42 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($265 to next deal) - confirm; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Phillips Peppermint 60pf Liter</t>
+          <t>Ciroc Vodka 750ml</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>087116048621</t>
+          <t>088076161863</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F209" t="n">
-        <v>38.6</v>
+        <v>38.2</v>
       </c>
       <c r="G209" t="n">
-        <v>-23</v>
+        <v>32</v>
       </c>
       <c r="H209" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="I209" t="n">
         <v>4</v>
@@ -13281,61 +13277,61 @@
         <v>1</v>
       </c>
       <c r="M209" t="n">
-        <v>4.91</v>
+        <v>22.05</v>
       </c>
       <c r="N209" t="n">
-        <v>59</v>
+        <v>265</v>
       </c>
       <c r="O209" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($59 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($265 to next deal) - confirm; Seasonal - last year ~4/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Angel's Envy Bourbon 375ml</t>
+          <t>Phillips Peppermint 60pf Liter</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>080480987787</t>
+          <t>087116048621</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="F210" t="n">
-        <v>40.7</v>
+        <v>38.6</v>
       </c>
       <c r="G210" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="H210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I210" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -13347,21 +13343,87 @@
         <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>17.39</v>
+        <v>4.91</v>
       </c>
       <c r="N210" t="n">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="O210" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($59 to next deal) - confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Angel's Envy Bourbon 375ml</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>080480987787</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Whisky/Whiskey</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>38</v>
+      </c>
+      <c r="F211" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" t="n">
+        <v>2</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>12</v>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="N211" t="n">
+        <v>209</v>
+      </c>
+      <c r="O211" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
+        <is>
           <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
-      <c r="S210" t="inlineStr">
+      <c r="S211" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($209 to next deal) - confirm</t>
         </is>
@@ -22705,7 +22767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23286,12 +23348,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jim Beam Bourbon 1.75L</t>
+          <t>Jim Beam Bourbon Liter</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>080686001102</t>
+          <t>080686001201</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -23305,43 +23367,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1212</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>11.8</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>128.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>24.39</v>
+        <v>15.86</v>
       </c>
       <c r="N10" t="n">
-        <v>146</v>
+        <v>381</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w)</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Wait for buy-month (Mar, Jun, Sep, Dec)</t>
@@ -23351,17 +23409,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jim Beam Bourbon Liter</t>
+          <t>Sauza Hornitos Plata 750ml</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>080686001201</t>
+          <t>080686835325</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23370,22 +23428,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="H11" t="n">
-        <v>8.199999999999999</v>
+        <v>33.2</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="K11" t="n">
         <v>24</v>
@@ -23394,30 +23452,30 @@
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>15.86</v>
+        <v>14.64</v>
       </c>
       <c r="N11" t="n">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="O11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Mar, Jun, Sep, Dec)</t>
+          <t>Wait for buy-month (Feb, Apr, May, Aug, Oct, Nov)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sauza Hornitos Plata 750ml</t>
+          <t>Sauza Hornitos Plata Tequila 1.75L</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>080686835325</t>
+          <t>080686835349</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23431,37 +23489,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="H12" t="n">
-        <v>33.2</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="J12" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="N12" t="n">
+        <v>519</v>
+      </c>
+      <c r="O12" t="n">
         <v>24</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="N12" t="n">
-        <v>351</v>
-      </c>
-      <c r="O12" t="n">
-        <v>39</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23473,73 +23531,73 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sauza Hornitos Plata Tequila 1.75L</t>
+          <t>Smirnoff Red White &amp; Berry Liter</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>080686835349</t>
+          <t>082000788096</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="H13" t="n">
-        <v>24</v>
+        <v>7.5</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>28.82</v>
+        <v>10.41</v>
       </c>
       <c r="N13" t="n">
-        <v>519</v>
+        <v>125</v>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, Apr, May, Aug, Oct, Nov)</t>
+          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Smirnoff Red White &amp; Berry Liter</t>
+          <t>Smirnoff Vodka Liter</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>082000788096</t>
+          <t>08200501</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -23549,41 +23607,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-14</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>7.5</v>
+        <v>32.8</v>
       </c>
       <c r="I14" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="J14" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>10.41</v>
+        <v>10.71</v>
       </c>
       <c r="N14" t="n">
-        <v>125</v>
+        <v>771</v>
       </c>
       <c r="O14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -23595,12 +23653,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Smirnoff Vodka Liter</t>
+          <t>Svedka Blue Raspberry Vodka 1.75L</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08200501</t>
+          <t>617768201176</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -23610,58 +23668,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>-4</v>
       </c>
       <c r="H15" t="n">
-        <v>32.8</v>
+        <v>10.2</v>
       </c>
       <c r="I15" t="n">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>10.71</v>
+        <v>14.71</v>
       </c>
       <c r="N15" t="n">
-        <v>771</v>
+        <v>177</v>
       </c>
       <c r="O15" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, Apr, Jun, Aug, Oct, Dec)</t>
+          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Svedka Blue Raspberry Vodka 1.75L</t>
+          <t>Svedka Vodka 100pf 1.75L</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>617768201176</t>
+          <t>088004071370</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -23675,37 +23733,37 @@
         </is>
       </c>
       <c r="E16" t="n">
+        <v>51</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>58</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>81</v>
+      </c>
+      <c r="J16" t="n">
+        <v>30</v>
+      </c>
+      <c r="K16" t="n">
         <v>48</v>
       </c>
-      <c r="F16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>27</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>12</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>14.71</v>
+        <v>14.62</v>
       </c>
       <c r="N16" t="n">
-        <v>177</v>
+        <v>702</v>
       </c>
       <c r="O16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23717,17 +23775,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Svedka Vodka 100pf 1.75L</t>
+          <t>Teremana Tequila Blanco 750ml</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>088004071370</t>
+          <t>850015640025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23736,101 +23794,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="I17" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="J17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>14.62</v>
+        <v>23.25</v>
       </c>
       <c r="N17" t="n">
-        <v>702</v>
+        <v>976</v>
       </c>
       <c r="O17" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Teremana Tequila Blanco 750ml</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>850015640025</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Agave</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>39</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>40</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>42</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>976</v>
-      </c>
-      <c r="O18" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
         <is>
           <t>Wait for buy-month (Mar, Jun, Sep, Dec)</t>
         </is>

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S173"/>
+  <dimension ref="A1:S172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6920,12 +6920,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Patron Reposado Tequila 375ml</t>
+          <t>Zarpado Blanco 1.75L</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>721733000951</t>
+          <t>810879022061</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6935,266 +6935,262 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F110" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G110" t="n">
-        <v>-25</v>
+        <v>18</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K110" t="n">
         <v>12</v>
       </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M110" t="n">
-        <v>21.11</v>
+        <v>30.83</v>
       </c>
       <c r="N110" t="n">
-        <v>253</v>
+        <v>370</v>
       </c>
       <c r="O110" t="n">
         <v>36</v>
       </c>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($253 to next deal) - confirm</t>
-        </is>
-      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Hendrick's Gin 750ml</t>
+          <t>Patron Reposado Tequila 375ml</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>083664990436</t>
+          <t>721733000951</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>42.75</v>
+        <v>9</v>
       </c>
       <c r="F111" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="G111" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="H111" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J111" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>24.75</v>
+        <v>21.11</v>
       </c>
       <c r="N111" t="n">
-        <v>148</v>
+        <v>253</v>
       </c>
       <c r="O111" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Sep) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($148 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($253 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Smirnoff Vodka Traveler</t>
+          <t>Hendrick's Gin 750ml</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>08295004</t>
+          <t>083664990436</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>567</v>
+        <v>42.75</v>
       </c>
       <c r="F112" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="G112" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="H112" t="n">
-        <v>97.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I112" t="n">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="J112" t="n">
-        <v>134</v>
+        <v>9</v>
       </c>
       <c r="K112" t="n">
-        <v>348</v>
+        <v>6</v>
       </c>
       <c r="L112" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>7.66</v>
+        <v>24.75</v>
       </c>
       <c r="N112" t="n">
-        <v>2666</v>
+        <v>148</v>
       </c>
       <c r="O112" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Sep) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($2,666 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($148 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Elijah Craig BBN Small Batch 94 750ml</t>
+          <t>Smirnoff Vodka Traveler</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>096749000067</t>
+          <t>08295004</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>120</v>
+        <v>567</v>
       </c>
       <c r="F113" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G113" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H113" t="n">
-        <v>24.8</v>
+        <v>97.5</v>
       </c>
       <c r="I113" t="n">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="J113" t="n">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="K113" t="n">
-        <v>72</v>
+        <v>348</v>
       </c>
       <c r="L113" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="M113" t="n">
-        <v>18.56</v>
+        <v>7.66</v>
       </c>
       <c r="N113" t="n">
-        <v>1336</v>
+        <v>2666</v>
       </c>
       <c r="O113" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Jun, Jul, Sep, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,336 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($2,666 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>St Germain Elderflower Liqueur 375ml</t>
+          <t>Elijah Craig BBN Small Batch 94 750ml</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>080480006662</t>
+          <t>096749000067</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7203,64 +7199,64 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="F114" t="n">
         <v>5.6</v>
       </c>
       <c r="G114" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="H114" t="n">
-        <v>7.8</v>
+        <v>24.8</v>
       </c>
       <c r="I114" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J114" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K114" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M114" t="n">
-        <v>12.17</v>
+        <v>18.56</v>
       </c>
       <c r="N114" t="n">
-        <v>584</v>
+        <v>1336</v>
       </c>
       <c r="O114" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Jun, Jul, Sep, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($584 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,336 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Seagrams Extra Dry Gin 1.75L</t>
+          <t>St Germain Elderflower Liqueur 375ml</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>080432401262</t>
+          <t>080480006662</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7269,64 +7265,64 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="F115" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G115" t="n">
-        <v>-22</v>
+        <v>-12</v>
       </c>
       <c r="H115" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I115" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J115" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K115" t="n">
         <v>48</v>
       </c>
       <c r="L115" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M115" t="n">
-        <v>11.02</v>
+        <v>12.17</v>
       </c>
       <c r="N115" t="n">
-        <v>529</v>
+        <v>584</v>
       </c>
       <c r="O115" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($529 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($584 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>St Germain Elderflower Liqueur 750ml</t>
+          <t>Seagrams Extra Dry Gin 1.75L</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>080480007379</t>
+          <t>080432401262</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7335,22 +7331,22 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="F116" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G116" t="n">
-        <v>14</v>
+        <v>-22</v>
       </c>
       <c r="H116" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="I116" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="J116" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K116" t="n">
         <v>48</v>
@@ -7359,101 +7355,101 @@
         <v>8</v>
       </c>
       <c r="M116" t="n">
-        <v>21.86</v>
+        <v>11.02</v>
       </c>
       <c r="N116" t="n">
-        <v>1049</v>
+        <v>529</v>
       </c>
       <c r="O116" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,049 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($529 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>New Amsterdam Apple Vodka 1.75L</t>
+          <t>St Germain Elderflower Liqueur 750ml</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>085000024881</t>
+          <t>080480007379</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F117" t="n">
         <v>5.8</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H117" t="n">
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K117" t="n">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="L117" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="M117" t="n">
-        <v>15.55</v>
+        <v>21.86</v>
       </c>
       <c r="N117" t="n">
-        <v>1960</v>
+        <v>1049</v>
       </c>
       <c r="O117" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,960 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,049 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Burnett's Vodka 1.75L</t>
+          <t>New Amsterdam Apple Vodka 1.75L</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>096749200313</t>
+          <t>085000024881</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7463,68 +7459,68 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="F118" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="G118" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>32.8</v>
+        <v>3.5</v>
       </c>
       <c r="I118" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="L118" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="M118" t="n">
-        <v>10.13</v>
+        <v>15.55</v>
       </c>
       <c r="N118" t="n">
-        <v>122</v>
+        <v>1960</v>
       </c>
       <c r="O118" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($122 to next deal) - confirm; Seasonal - last year ~33/wk vs 15 now, buy ahead?</t>
+          <t>Buy-month stock-up ($1,960 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Seagrams Lime Gin Liter</t>
+          <t>Burnett's Vodka 1.75L</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>080432401620</t>
+          <t>096749200313</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7533,125 +7529,125 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="F119" t="n">
         <v>6</v>
       </c>
       <c r="G119" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H119" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I119" t="n">
+        <v>30</v>
+      </c>
+      <c r="J119" t="n">
+        <v>23</v>
+      </c>
+      <c r="K119" t="n">
+        <v>12</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="N119" t="n">
+        <v>122</v>
+      </c>
+      <c r="O119" t="n">
         <v>40</v>
-      </c>
-      <c r="H119" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I119" t="n">
-        <v>24</v>
-      </c>
-      <c r="J119" t="n">
-        <v>20</v>
-      </c>
-      <c r="K119" t="n">
-        <v>72</v>
-      </c>
-      <c r="L119" t="n">
-        <v>6</v>
-      </c>
-      <c r="M119" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="N119" t="n">
-        <v>674</v>
-      </c>
-      <c r="O119" t="n">
-        <v>38</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($674 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($122 to next deal) - confirm; Seasonal - last year ~33/wk vs 15 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>New Amsterdam Lemon 1.75L</t>
+          <t>Seagrams Lime Gin Liter</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>085000026540</t>
+          <t>080432401620</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E120" t="n">
+        <v>60</v>
+      </c>
+      <c r="F120" t="n">
+        <v>6</v>
+      </c>
+      <c r="G120" t="n">
+        <v>40</v>
+      </c>
+      <c r="H120" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I120" t="n">
+        <v>24</v>
+      </c>
+      <c r="J120" t="n">
         <v>20</v>
       </c>
-      <c r="F120" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G120" t="n">
-        <v>5</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I120" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
       <c r="K120" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="L120" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M120" t="n">
-        <v>15.35</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="N120" t="n">
-        <v>1934</v>
+        <v>674</v>
       </c>
       <c r="O120" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,934 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($674 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>New Amsterdam Vodka 200ml</t>
+          <t>New Amsterdam Lemon 1.75L</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>085000019474</t>
+          <t>085000026540</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7665,45 +7661,49 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F121" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="G121" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H121" t="n">
-        <v>10.2</v>
+        <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="M121" t="n">
-        <v>3.99</v>
+        <v>15.35</v>
       </c>
       <c r="N121" t="n">
-        <v>96</v>
+        <v>1934</v>
       </c>
       <c r="O121" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($1,934 to next deal) - confirm</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9292,41 +9292,41 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dos Amigos Tequila Reposado 750ml</t>
+          <t>Smirnoff Strawberry &amp; Rose Zero Sugar 750ml</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>698450104463</t>
+          <t>082000790815</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>New France Wine Co, Inc</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F146" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="G146" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K146" t="n">
         <v>12</v>
@@ -9335,79 +9335,79 @@
         <v>1</v>
       </c>
       <c r="M146" t="n">
-        <v>21.99</v>
+        <v>8</v>
       </c>
       <c r="N146" t="n">
-        <v>264</v>
+        <v>96</v>
       </c>
       <c r="O146" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Smirnoff Strawberry &amp; Rose Zero Sugar 750ml</t>
+          <t>Bulleit 95 Rye Whiskey 1.75L</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>082000790815</t>
+          <t>082000766070</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="F147" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="G147" t="n">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="H147" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="I147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J147" t="n">
         <v>4</v>
       </c>
       <c r="K147" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L147" t="n">
         <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>8</v>
+        <v>38.05</v>
       </c>
       <c r="N147" t="n">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="O147" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
@@ -9417,19 +9417,19 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Bulleit 95 Rye Whiskey 1.75L</t>
+          <t>Crown Royal Canadian Liter</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>082000766070</t>
+          <t>087000007246</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9443,37 +9443,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F148" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="G148" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="H148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J148" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L148" t="n">
         <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>38.05</v>
+        <v>26.26</v>
       </c>
       <c r="N148" t="n">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="O148" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr">
@@ -9483,45 +9483,45 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($315 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Crown Royal Canadian Liter</t>
+          <t>Patron Citronge 750ml</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>087000007246</t>
+          <t>721733000043</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="F149" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="G149" t="n">
         <v>-15</v>
       </c>
       <c r="H149" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -9533,40 +9533,40 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>26.26</v>
+        <v>14.37</v>
       </c>
       <c r="N149" t="n">
-        <v>315</v>
+        <v>172</v>
       </c>
       <c r="O149" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($315 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($172 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Patron Citronge 750ml</t>
+          <t>Larceny Bourbon 750ml</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>721733000043</t>
+          <t>096749031559</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9575,19 +9575,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F150" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="G150" t="n">
-        <v>-15</v>
+        <v>-35</v>
       </c>
       <c r="H150" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -9599,106 +9599,106 @@
         <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>14.37</v>
+        <v>17.42</v>
       </c>
       <c r="N150" t="n">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="O150" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($172 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Larceny Bourbon 750ml</t>
+          <t>New Amsterdam Tangerine 1.75L</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>096749031559</t>
+          <t>085000034835</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="F151" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G151" t="n">
-        <v>-35</v>
+        <v>-50</v>
       </c>
       <c r="H151" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M151" t="n">
-        <v>17.42</v>
+        <v>15.21</v>
       </c>
       <c r="N151" t="n">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="O151" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($274 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>New Amsterdam Tangerine 1.75L</t>
+          <t>George Dickel No 12 750ml</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>085000034835</t>
+          <t>088076006232</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9707,85 +9707,85 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F152" t="n">
-        <v>15</v>
+        <v>15.7</v>
       </c>
       <c r="G152" t="n">
-        <v>-50</v>
+        <v>35</v>
       </c>
       <c r="H152" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M152" t="n">
-        <v>15.21</v>
+        <v>18.82</v>
       </c>
       <c r="N152" t="n">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="O152" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($274 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($226 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>George Dickel No 12 750ml</t>
+          <t>Phillips Peach Schnapps Liter</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>088076006232</t>
+          <t>087116018310</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F153" t="n">
         <v>15.7</v>
       </c>
       <c r="G153" t="n">
-        <v>35</v>
+        <v>-25</v>
       </c>
       <c r="H153" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -9797,101 +9797,101 @@
         <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>18.82</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N153" t="n">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="O153" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($226 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($107 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Phillips Peach Schnapps Liter</t>
+          <t>Chopin Vodka 750ml</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>087116018310</t>
+          <t>852935001153</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F154" t="n">
-        <v>15.7</v>
+        <v>16.1</v>
       </c>
       <c r="G154" t="n">
-        <v>-25</v>
+        <v>-43</v>
       </c>
       <c r="H154" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L154" t="n">
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>8.949999999999999</v>
+        <v>19.13</v>
       </c>
       <c r="N154" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="O154" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($107 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Chopin Vodka 750ml</t>
+          <t>Absolut Citron Vodka Liter</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>852935001153</t>
+          <t>835229001404</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9905,85 +9905,85 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="F155" t="n">
-        <v>16.1</v>
+        <v>17.3</v>
       </c>
       <c r="G155" t="n">
-        <v>-43</v>
+        <v>-12</v>
       </c>
       <c r="H155" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>19.13</v>
+        <v>19.58</v>
       </c>
       <c r="N155" t="n">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="O155" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($235 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Absolut Citron Vodka Liter</t>
+          <t>Buchanans 12 Yr Scotch 750ml</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>835229001404</t>
+          <t>088110955328</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="F156" t="n">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="G156" t="n">
-        <v>-12</v>
+        <v>40</v>
       </c>
       <c r="H156" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="I156" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -9995,61 +9995,61 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>19.58</v>
+        <v>26.73</v>
       </c>
       <c r="N156" t="n">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="O156" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jun, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($235 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Buchanans 12 Yr Scotch 750ml</t>
+          <t>Phillips Blackberry Brandy Liter</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>088110955328</t>
+          <t>087116048188</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="F157" t="n">
-        <v>17.7</v>
+        <v>19.1</v>
       </c>
       <c r="G157" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="H157" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -10061,40 +10061,40 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>26.73</v>
+        <v>10.4</v>
       </c>
       <c r="N157" t="n">
-        <v>321</v>
+        <v>125</v>
       </c>
       <c r="O157" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jun, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($125 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Phillips Blackberry Brandy Liter</t>
+          <t>Windsor Apple 1.75L</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>087116048188</t>
+          <t>084279007403</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10103,64 +10103,64 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F158" t="n">
         <v>19.1</v>
       </c>
       <c r="G158" t="n">
-        <v>73</v>
+        <v>-28</v>
       </c>
       <c r="H158" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I158" t="n">
         <v>5</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K158" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>10.4</v>
+        <v>15.34</v>
       </c>
       <c r="N158" t="n">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="O158" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($125 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Windsor Apple 1.75L</t>
+          <t>Phillips Amaretto Liter</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>084279007403</t>
+          <t>087116048249</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10169,64 +10169,64 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F159" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="G159" t="n">
-        <v>-28</v>
+        <v>-16</v>
       </c>
       <c r="H159" t="n">
         <v>3.2</v>
       </c>
       <c r="I159" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L159" t="n">
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>15.34</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N159" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="O159" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($110 to next deal) - confirm; Seasonal - last year ~3/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Phillips Amaretto Liter</t>
+          <t>Phillips Peppermint 60pf Traveler</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>087116048249</t>
+          <t>087116018693</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10235,19 +10235,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F160" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="G160" t="n">
-        <v>-16</v>
+        <v>29</v>
       </c>
       <c r="H160" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>9.140000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="N160" t="n">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="O160" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
@@ -10275,19 +10275,19 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($110 to next deal) - confirm; Seasonal - last year ~3/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Phillips Peppermint 60pf Traveler</t>
+          <t>Phillips Rootbeer Schnapps Liter</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>087116018693</t>
+          <t>087116034617</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10301,19 +10301,19 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F161" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G161" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H161" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I161" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -10325,13 +10325,13 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>7.01</v>
+        <v>9.07</v>
       </c>
       <c r="N161" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="O161" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr">
@@ -10341,48 +10341,48 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Phillips Rootbeer Schnapps Liter</t>
+          <t>Absolut Vodka 750ml</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>087116034617</t>
+          <t>835229000308</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5</v>
+        <v>409</v>
       </c>
       <c r="F162" t="n">
-        <v>21.4</v>
+        <v>23.4</v>
       </c>
       <c r="G162" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H162" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K162" t="n">
         <v>12</v>
@@ -10391,64 +10391,64 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>9.07</v>
+        <v>15.17</v>
       </c>
       <c r="N162" t="n">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="O162" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($182 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Absolut Vodka 750ml</t>
+          <t>Phillips Peppermint 80pf Liter</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>835229000308</t>
+          <t>087116048645</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>409</v>
+        <v>69</v>
       </c>
       <c r="F163" t="n">
-        <v>23.4</v>
+        <v>26.9</v>
       </c>
       <c r="G163" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H163" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="I163" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>12</v>
@@ -10457,40 +10457,40 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>15.17</v>
+        <v>9.6</v>
       </c>
       <c r="N163" t="n">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="O163" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($182 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Phillips Peppermint 80pf Liter</t>
+          <t>Crown Royal Vanilla 1.75L</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>087116048645</t>
+          <t>082000776611</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10499,148 +10499,148 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>26.9</v>
+        <v>28.8</v>
       </c>
       <c r="G164" t="n">
-        <v>22</v>
+        <v>-16</v>
       </c>
       <c r="H164" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>9.6</v>
+        <v>36.98</v>
       </c>
       <c r="N164" t="n">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="O164" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Crown Royal Vanilla 1.75L</t>
+          <t>Absolut Lime Vodka Liter</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>082000776611</t>
+          <t>835229010284</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="F165" t="n">
-        <v>28.8</v>
+        <v>30.8</v>
       </c>
       <c r="G165" t="n">
         <v>-16</v>
       </c>
       <c r="H165" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="I165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L165" t="n">
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>36.98</v>
+        <v>19.21</v>
       </c>
       <c r="N165" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="O165" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Absolut Lime Vodka Liter</t>
+          <t>Captain Morgan 100 Proof Liter</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>835229010284</t>
+          <t>082000741992</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="F166" t="n">
-        <v>30.8</v>
+        <v>33.9</v>
       </c>
       <c r="G166" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="H166" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I166" t="n">
         <v>2</v>
@@ -10655,18 +10655,18 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>19.21</v>
+        <v>19.27</v>
       </c>
       <c r="N166" t="n">
         <v>231</v>
       </c>
       <c r="O166" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -10678,17 +10678,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Captain Morgan 100 Proof Liter</t>
+          <t>Ciroc Peach Vodka 750ml</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>082000741992</t>
+          <t>088076177406</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10697,19 +10697,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F167" t="n">
-        <v>33.9</v>
+        <v>34.3</v>
       </c>
       <c r="G167" t="n">
-        <v>25</v>
+        <v>-33</v>
       </c>
       <c r="H167" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -10721,13 +10721,13 @@
         <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>19.27</v>
+        <v>21.53</v>
       </c>
       <c r="N167" t="n">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="O167" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr">
@@ -10737,19 +10737,19 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ciroc Peach Vodka 750ml</t>
+          <t>Absolut Pears Vodka Liter</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>088076177406</t>
+          <t>835229001343</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10759,23 +10759,23 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="F168" t="n">
-        <v>34.3</v>
+        <v>37.5</v>
       </c>
       <c r="G168" t="n">
-        <v>-33</v>
+        <v>-13</v>
       </c>
       <c r="H168" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -10787,61 +10787,61 @@
         <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>21.53</v>
+        <v>19.22</v>
       </c>
       <c r="N168" t="n">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="O168" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Absolut Pears Vodka Liter</t>
+          <t>Crown Royal Regal Apple Liter</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>835229001343</t>
+          <t>082000771586</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>140</v>
+        <v>292</v>
       </c>
       <c r="F169" t="n">
-        <v>37.5</v>
+        <v>40.4</v>
       </c>
       <c r="G169" t="n">
-        <v>-13</v>
+        <v>-25</v>
       </c>
       <c r="H169" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -10853,35 +10853,35 @@
         <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>19.22</v>
+        <v>26.6</v>
       </c>
       <c r="N169" t="n">
-        <v>231</v>
+        <v>319</v>
       </c>
       <c r="O169" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($319 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Crown Royal Regal Apple Liter</t>
+          <t>Angel's Envy Bourbon 375ml</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>082000771586</t>
+          <t>080480987787</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10891,23 +10891,23 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>292</v>
+        <v>38</v>
       </c>
       <c r="F170" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
       <c r="G170" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -10919,61 +10919,61 @@
         <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>26.6</v>
+        <v>17.39</v>
       </c>
       <c r="N170" t="n">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="O170" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($319 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Angel's Envy Bourbon 375ml</t>
+          <t>Ciroc Vodka 750ml</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>080480987787</t>
+          <t>088076161863</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="F171" t="n">
-        <v>40.7</v>
+        <v>43.5</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H171" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -10985,58 +10985,58 @@
         <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>17.39</v>
+        <v>21.76</v>
       </c>
       <c r="N171" t="n">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="O171" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($261 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ciroc Vodka 750ml</t>
+          <t>Phillips Peppermint 60pf Liter</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>088076161863</t>
+          <t>087116048621</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="F172" t="n">
-        <v>43.5</v>
+        <v>49.6</v>
       </c>
       <c r="G172" t="n">
-        <v>44</v>
+        <v>-38</v>
       </c>
       <c r="H172" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="I172" t="n">
         <v>3</v>
@@ -11051,87 +11051,21 @@
         <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>21.76</v>
+        <v>4.91</v>
       </c>
       <c r="N172" t="n">
-        <v>261</v>
+        <v>59</v>
       </c>
       <c r="O172" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($261 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Phillips Peppermint 60pf Liter</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>087116048621</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Schnapps</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>81</v>
-      </c>
-      <c r="F173" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G173" t="n">
-        <v>-38</v>
-      </c>
-      <c r="H173" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I173" t="n">
-        <v>3</v>
-      </c>
-      <c r="J173" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" t="n">
-        <v>12</v>
-      </c>
-      <c r="L173" t="n">
-        <v>1</v>
-      </c>
-      <c r="M173" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="N173" t="n">
-        <v>59</v>
-      </c>
-      <c r="O173" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($59 to next deal) - confirm</t>
         </is>
@@ -11148,7 +11082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15109,41 +15043,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dos Amigos Tequila Reposado 750ml</t>
+          <t>Smirnoff Strawberry &amp; Rose Zero Sugar 750ml</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>698450104463</t>
+          <t>082000790815</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>New France Wine Co, Inc</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F61" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="G61" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
         <v>12</v>
@@ -15152,79 +15086,79 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>21.99</v>
+        <v>8</v>
       </c>
       <c r="N61" t="n">
-        <v>264</v>
+        <v>96</v>
       </c>
       <c r="O61" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Smirnoff Strawberry &amp; Rose Zero Sugar 750ml</t>
+          <t>Bulleit 95 Rye Whiskey 1.75L</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>082000790815</t>
+          <t>082000766070</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="F62" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="G62" t="n">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="H62" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>8</v>
+        <v>38.05</v>
       </c>
       <c r="N62" t="n">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="O62" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
@@ -15234,19 +15168,19 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bulleit 95 Rye Whiskey 1.75L</t>
+          <t>Crown Royal Canadian Liter</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>082000766070</t>
+          <t>087000007246</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15260,37 +15194,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="F63" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="G63" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="H63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L63" t="n">
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>38.05</v>
+        <v>26.26</v>
       </c>
       <c r="N63" t="n">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="O63" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
@@ -15300,45 +15234,45 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($315 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Crown Royal Canadian Liter</t>
+          <t>Patron Citronge 750ml</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>087000007246</t>
+          <t>721733000043</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="F64" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="G64" t="n">
         <v>-15</v>
       </c>
       <c r="H64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -15350,40 +15284,40 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>26.26</v>
+        <v>14.37</v>
       </c>
       <c r="N64" t="n">
-        <v>315</v>
+        <v>172</v>
       </c>
       <c r="O64" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($315 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($172 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Patron Citronge 750ml</t>
+          <t>Larceny Bourbon 750ml</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>721733000043</t>
+          <t>096749031559</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -15392,19 +15326,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F65" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="G65" t="n">
-        <v>-15</v>
+        <v>-35</v>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -15416,106 +15350,106 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>14.37</v>
+        <v>17.42</v>
       </c>
       <c r="N65" t="n">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="O65" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($172 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Larceny Bourbon 750ml</t>
+          <t>New Amsterdam Tangerine 1.75L</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>096749031559</t>
+          <t>085000034835</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G66" t="n">
-        <v>-35</v>
+        <v>-50</v>
       </c>
       <c r="H66" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M66" t="n">
-        <v>17.42</v>
+        <v>15.21</v>
       </c>
       <c r="N66" t="n">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="O66" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~10/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($274 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>New Amsterdam Tangerine 1.75L</t>
+          <t>George Dickel No 12 750ml</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>085000034835</t>
+          <t>088076006232</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -15524,85 +15458,85 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F67" t="n">
-        <v>15</v>
+        <v>15.7</v>
       </c>
       <c r="G67" t="n">
-        <v>-50</v>
+        <v>35</v>
       </c>
       <c r="H67" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>15.21</v>
+        <v>18.82</v>
       </c>
       <c r="N67" t="n">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="O67" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>In buy-month (May, Jul) - stock up ~43wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($274 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($226 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>George Dickel No 12 750ml</t>
+          <t>Phillips Peach Schnapps Liter</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>088076006232</t>
+          <t>087116018310</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F68" t="n">
         <v>15.7</v>
       </c>
       <c r="G68" t="n">
-        <v>35</v>
+        <v>-25</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -15614,101 +15548,101 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>18.82</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="O68" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($226 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($107 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Phillips Peach Schnapps Liter</t>
+          <t>Chopin Vodka 750ml</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>087116018310</t>
+          <t>852935001153</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>15.7</v>
+        <v>16.1</v>
       </c>
       <c r="G69" t="n">
-        <v>-25</v>
+        <v>-43</v>
       </c>
       <c r="H69" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>8.949999999999999</v>
+        <v>19.13</v>
       </c>
       <c r="N69" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="O69" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($107 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Chopin Vodka 750ml</t>
+          <t>Absolut Citron Vodka Liter</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>852935001153</t>
+          <t>835229001404</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15722,85 +15656,85 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="F70" t="n">
-        <v>16.1</v>
+        <v>17.3</v>
       </c>
       <c r="G70" t="n">
-        <v>-43</v>
+        <v>-12</v>
       </c>
       <c r="H70" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>19.13</v>
+        <v>19.58</v>
       </c>
       <c r="N70" t="n">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="O70" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($235 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Absolut Citron Vodka Liter</t>
+          <t>Buchanans 12 Yr Scotch 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>835229001404</t>
+          <t>088110955328</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="F71" t="n">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="G71" t="n">
-        <v>-12</v>
+        <v>40</v>
       </c>
       <c r="H71" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -15812,61 +15746,61 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>19.58</v>
+        <v>26.73</v>
       </c>
       <c r="N71" t="n">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="O71" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jun, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($235 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Buchanans 12 Yr Scotch 750ml</t>
+          <t>Phillips Blackberry Brandy Liter</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>088110955328</t>
+          <t>087116048188</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="F72" t="n">
-        <v>17.7</v>
+        <v>19.1</v>
       </c>
       <c r="G72" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="H72" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -15878,40 +15812,40 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>26.73</v>
+        <v>10.4</v>
       </c>
       <c r="N72" t="n">
-        <v>321</v>
+        <v>125</v>
       </c>
       <c r="O72" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jun, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($125 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Phillips Blackberry Brandy Liter</t>
+          <t>Windsor Apple 1.75L</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>087116048188</t>
+          <t>084279007403</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -15920,64 +15854,64 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F73" t="n">
         <v>19.1</v>
       </c>
       <c r="G73" t="n">
-        <v>73</v>
+        <v>-28</v>
       </c>
       <c r="H73" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I73" t="n">
         <v>5</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>10.4</v>
+        <v>15.34</v>
       </c>
       <c r="N73" t="n">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="O73" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($125 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Windsor Apple 1.75L</t>
+          <t>Phillips Amaretto Liter</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>084279007403</t>
+          <t>087116048249</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -15986,64 +15920,64 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F74" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="G74" t="n">
-        <v>-28</v>
+        <v>-16</v>
       </c>
       <c r="H74" t="n">
         <v>3.2</v>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>15.34</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="O74" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($110 to next deal) - confirm; Seasonal - last year ~3/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Phillips Amaretto Liter</t>
+          <t>Phillips Peppermint 60pf Traveler</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>087116048249</t>
+          <t>087116018693</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -16052,19 +15986,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F75" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="G75" t="n">
-        <v>-16</v>
+        <v>29</v>
       </c>
       <c r="H75" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -16076,13 +16010,13 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>9.140000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="N75" t="n">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="O75" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
@@ -16092,19 +16026,19 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($110 to next deal) - confirm; Seasonal - last year ~3/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Phillips Peppermint 60pf Traveler</t>
+          <t>Phillips Rootbeer Schnapps Liter</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>087116018693</t>
+          <t>087116034617</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -16118,19 +16052,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G76" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H76" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -16142,13 +16076,13 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>7.01</v>
+        <v>9.07</v>
       </c>
       <c r="N76" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="O76" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
@@ -16158,48 +16092,48 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Phillips Rootbeer Schnapps Liter</t>
+          <t>Absolut Vodka 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>087116034617</t>
+          <t>835229000308</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5</v>
+        <v>409</v>
       </c>
       <c r="F77" t="n">
-        <v>21.4</v>
+        <v>23.4</v>
       </c>
       <c r="G77" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K77" t="n">
         <v>12</v>
@@ -16208,64 +16142,64 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>9.07</v>
+        <v>15.17</v>
       </c>
       <c r="N77" t="n">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="O77" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($182 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Absolut Vodka 750ml</t>
+          <t>Phillips Peppermint 80pf Liter</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>835229000308</t>
+          <t>087116048645</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>409</v>
+        <v>69</v>
       </c>
       <c r="F78" t="n">
-        <v>23.4</v>
+        <v>26.9</v>
       </c>
       <c r="G78" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H78" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
         <v>12</v>
@@ -16274,40 +16208,40 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>15.17</v>
+        <v>9.6</v>
       </c>
       <c r="N78" t="n">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="O78" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($182 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Phillips Peppermint 80pf Liter</t>
+          <t>Crown Royal Vanilla 1.75L</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>087116048645</t>
+          <t>082000776611</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Schnapps</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -16316,148 +16250,148 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F79" t="n">
-        <v>26.9</v>
+        <v>28.8</v>
       </c>
       <c r="G79" t="n">
-        <v>22</v>
+        <v>-16</v>
       </c>
       <c r="H79" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L79" t="n">
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>9.6</v>
+        <v>36.98</v>
       </c>
       <c r="N79" t="n">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="O79" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Crown Royal Vanilla 1.75L</t>
+          <t>Absolut Lime Vodka Liter</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>082000776611</t>
+          <t>835229010284</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="F80" t="n">
-        <v>28.8</v>
+        <v>30.8</v>
       </c>
       <c r="G80" t="n">
         <v>-16</v>
       </c>
       <c r="H80" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>36.98</v>
+        <v>19.21</v>
       </c>
       <c r="N80" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="O80" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($222 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Absolut Lime Vodka Liter</t>
+          <t>Captain Morgan 100 Proof Liter</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>835229010284</t>
+          <t>082000741992</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="F81" t="n">
-        <v>30.8</v>
+        <v>33.9</v>
       </c>
       <c r="G81" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="H81" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I81" t="n">
         <v>2</v>
@@ -16472,18 +16406,18 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>19.21</v>
+        <v>19.27</v>
       </c>
       <c r="N81" t="n">
         <v>231</v>
       </c>
       <c r="O81" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -16495,17 +16429,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Captain Morgan 100 Proof Liter</t>
+          <t>Ciroc Peach Vodka 750ml</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>082000741992</t>
+          <t>088076177406</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16514,19 +16448,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F82" t="n">
-        <v>33.9</v>
+        <v>34.3</v>
       </c>
       <c r="G82" t="n">
-        <v>25</v>
+        <v>-33</v>
       </c>
       <c r="H82" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -16538,13 +16472,13 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>19.27</v>
+        <v>21.53</v>
       </c>
       <c r="N82" t="n">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="O82" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
@@ -16554,19 +16488,19 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ciroc Peach Vodka 750ml</t>
+          <t>Absolut Pears Vodka Liter</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>088076177406</t>
+          <t>835229001343</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -16576,23 +16510,23 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="F83" t="n">
-        <v>34.3</v>
+        <v>37.5</v>
       </c>
       <c r="G83" t="n">
-        <v>-33</v>
+        <v>-13</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -16604,61 +16538,61 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>21.53</v>
+        <v>19.22</v>
       </c>
       <c r="N83" t="n">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="O83" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($258 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Absolut Pears Vodka Liter</t>
+          <t>Crown Royal Regal Apple Liter</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>835229001343</t>
+          <t>082000771586</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>140</v>
+        <v>292</v>
       </c>
       <c r="F84" t="n">
-        <v>37.5</v>
+        <v>40.4</v>
       </c>
       <c r="G84" t="n">
-        <v>-13</v>
+        <v>-25</v>
       </c>
       <c r="H84" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -16670,35 +16604,35 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>19.22</v>
+        <v>26.6</v>
       </c>
       <c r="N84" t="n">
-        <v>231</v>
+        <v>319</v>
       </c>
       <c r="O84" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($231 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($319 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Crown Royal Regal Apple Liter</t>
+          <t>Angel's Envy Bourbon 375ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>082000771586</t>
+          <t>080480987787</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -16708,23 +16642,23 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>292</v>
+        <v>38</v>
       </c>
       <c r="F85" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
       <c r="G85" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -16736,61 +16670,61 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>26.6</v>
+        <v>17.39</v>
       </c>
       <c r="N85" t="n">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="O85" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($319 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Angel's Envy Bourbon 375ml</t>
+          <t>Ciroc Vodka 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>080480987787</t>
+          <t>088076161863</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="F86" t="n">
-        <v>40.7</v>
+        <v>43.5</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H86" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -16802,58 +16736,58 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>17.39</v>
+        <v>21.76</v>
       </c>
       <c r="N86" t="n">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="O86" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($261 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ciroc Vodka 750ml</t>
+          <t>Phillips Peppermint 60pf Liter</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>088076161863</t>
+          <t>087116048621</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Schnapps</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="F87" t="n">
-        <v>43.5</v>
+        <v>49.6</v>
       </c>
       <c r="G87" t="n">
-        <v>44</v>
+        <v>-38</v>
       </c>
       <c r="H87" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="I87" t="n">
         <v>3</v>
@@ -16868,87 +16802,21 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>21.76</v>
+        <v>4.91</v>
       </c>
       <c r="N87" t="n">
-        <v>261</v>
+        <v>59</v>
       </c>
       <c r="O87" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($261 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Phillips Peppermint 60pf Liter</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>087116048621</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Schnapps</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>81</v>
-      </c>
-      <c r="F88" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G88" t="n">
-        <v>-38</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I88" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>12</v>
-      </c>
-      <c r="L88" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="N88" t="n">
-        <v>59</v>
-      </c>
-      <c r="O88" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($59 to next deal) - confirm</t>
         </is>
@@ -17827,11 +17695,7 @@
       <c r="O15" t="n">
         <v>31</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18055,11 +17919,7 @@
       <c r="O19" t="n">
         <v>54</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">

--- a/data/Spirits Recommended Order.xlsx
+++ b/data/Spirits Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5160,21 +5160,25 @@
         <v>185</v>
       </c>
       <c r="K79" t="n">
-        <v>120</v>
+        <v>840</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M79" t="n">
         <v>0.67</v>
       </c>
       <c r="N79" t="n">
-        <v>80</v>
+        <v>563</v>
       </c>
       <c r="O79" t="n">
         <v>55</v>
       </c>
-      <c r="Q79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5472,11 +5476,7 @@
       <c r="O84" t="n">
         <v>16</v>
       </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w)</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
@@ -6941,113 +6941,122 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BuzzBallz Berry Cherry Limeade 187ml</t>
+          <t>Smirnoff Vodka Liter</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>857674007985</t>
+          <t>08200501</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>792</v>
+        <v>173</v>
       </c>
       <c r="F108" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G108" t="n">
-        <v>-12</v>
+        <v>6</v>
       </c>
       <c r="H108" t="n">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="I108" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="J108" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="K108" t="n">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="L108" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>0.61</v>
+        <v>10.58</v>
       </c>
       <c r="N108" t="n">
-        <v>15</v>
+        <v>1396</v>
       </c>
       <c r="O108" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($1,396 to next deal) - confirm</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Smirnoff Vodka Liter</t>
+          <t>Captain Morgan Spiced Rum 1.75L</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>08200501</t>
+          <t>082000759102</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>173</v>
+        <v>1042</v>
       </c>
       <c r="F109" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G109" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="H109" t="n">
-        <v>41</v>
+        <v>240.2</v>
       </c>
       <c r="I109" t="n">
+        <v>59</v>
+      </c>
+      <c r="J109" t="n">
+        <v>59</v>
+      </c>
+      <c r="K109" t="n">
+        <v>738</v>
+      </c>
+      <c r="L109" t="n">
+        <v>123</v>
+      </c>
+      <c r="M109" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="N109" t="n">
+        <v>13245</v>
+      </c>
+      <c r="O109" t="n">
         <v>34</v>
-      </c>
-      <c r="J109" t="n">
-        <v>30</v>
-      </c>
-      <c r="K109" t="n">
-        <v>132</v>
-      </c>
-      <c r="L109" t="n">
-        <v>11</v>
-      </c>
-      <c r="M109" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1396</v>
-      </c>
-      <c r="O109" t="n">
-        <v>41</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
@@ -7057,75 +7066,71 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,396 to next deal) - confirm</t>
+          <t>Large buy ($13,245) - confirm; Buy-month stock-up ($13,245 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Captain Morgan Spiced Rum 1.75L</t>
+          <t>Aperol Aperitivo 750ml</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>082000759102</t>
+          <t>721059001311</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1042</v>
+        <v>194</v>
       </c>
       <c r="F110" t="n">
         <v>5.1</v>
       </c>
       <c r="G110" t="n">
-        <v>-3</v>
+        <v>-19</v>
       </c>
       <c r="H110" t="n">
-        <v>240.2</v>
+        <v>32</v>
       </c>
       <c r="I110" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="J110" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="K110" t="n">
-        <v>738</v>
+        <v>6</v>
       </c>
       <c r="L110" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>17.95</v>
+        <v>15.8</v>
       </c>
       <c r="N110" t="n">
-        <v>13245</v>
+        <v>95</v>
       </c>
       <c r="O110" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>Large buy ($13,245) - confirm; Buy-month stock-up ($13,245 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10760,41 +10765,41 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Gray Duck Liter</t>
+          <t>Bulleit 95 Rye Whiskey 750ml</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>860199002601</t>
+          <t>082000752967</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="F166" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="G166" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H166" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="I166" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K166" t="n">
         <v>12</v>
@@ -10803,238 +10808,238 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>11.61</v>
+        <v>16.33</v>
       </c>
       <c r="N166" t="n">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="O166" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more; Seasonal - last year ~24/wk vs 11 now, buy ahead?</t>
+          <t>Buy-month stock-up ($196 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Bulleit 95 Rye Whiskey 750ml</t>
+          <t>Mi Campo Blanco 750ml</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>082000752967</t>
+          <t>086003272033</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F167" t="n">
         <v>9.9</v>
       </c>
       <c r="G167" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H167" t="n">
-        <v>14.5</v>
+        <v>13.2</v>
       </c>
       <c r="I167" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J167" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K167" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M167" t="n">
-        <v>16.33</v>
+        <v>12.47</v>
       </c>
       <c r="N167" t="n">
-        <v>196</v>
+        <v>598</v>
       </c>
       <c r="O167" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($196 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($598 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mi Campo Blanco 750ml</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>086003272033</t>
+          <t>085000434260</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Pre-Mix</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="F168" t="n">
         <v>9.9</v>
       </c>
       <c r="G168" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>13.2</v>
+        <v>8</v>
       </c>
       <c r="I168" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J168" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K168" t="n">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="L168" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="M168" t="n">
-        <v>12.47</v>
+        <v>8.25</v>
       </c>
       <c r="N168" t="n">
-        <v>598</v>
+        <v>1584</v>
       </c>
       <c r="O168" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (May, Aug) - stock up ~39wks to next deal</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($598 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,584 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Malibu Black Rum 1.75L</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>085000434260</t>
+          <t>089540520155</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F169" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="H169" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="L169" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="M169" t="n">
-        <v>8.25</v>
+        <v>19.67</v>
       </c>
       <c r="N169" t="n">
-        <v>1584</v>
+        <v>118</v>
       </c>
       <c r="O169" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr">
         <is>
-          <t>In buy-month (May, Aug) - stock up ~39wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,584 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($118 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Malibu Black Rum 1.75L</t>
+          <t>Canadian Club Traveler</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>089540520155</t>
+          <t>080686821434</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -11043,37 +11048,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F170" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="G170" t="n">
-        <v>-33</v>
+        <v>-8</v>
       </c>
       <c r="H170" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="I170" t="n">
+        <v>3</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>24</v>
+      </c>
+      <c r="L170" t="n">
         <v>2</v>
       </c>
-      <c r="J170" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" t="n">
-        <v>6</v>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
       <c r="M170" t="n">
-        <v>19.67</v>
+        <v>8.15</v>
       </c>
       <c r="N170" t="n">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="O170" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr">
@@ -11083,42 +11088,42 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($118 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($196 to next deal) - confirm; Seasonal - last year ~11/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Canadian Club Traveler</t>
+          <t>Don Julio Blanco 375ml</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>080686821434</t>
+          <t>674545000599</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F171" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G171" t="n">
-        <v>-8</v>
+        <v>-55</v>
       </c>
       <c r="H171" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="I171" t="n">
         <v>3</v>
@@ -11127,64 +11132,64 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>8.15</v>
+        <v>16.67</v>
       </c>
       <c r="N171" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="O171" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($196 to next deal) - confirm; Seasonal - last year ~11/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($200 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Don Julio Blanco 375ml</t>
+          <t>Svedka Vanilla Vodka 1.75L</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>674545000599</t>
+          <t>088004071929</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F172" t="n">
         <v>10.4</v>
       </c>
       <c r="G172" t="n">
-        <v>-55</v>
+        <v>-43</v>
       </c>
       <c r="H172" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
         <v>3</v>
@@ -11196,43 +11201,43 @@
         <v>12</v>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
-        <v>16.67</v>
+        <v>14.62</v>
       </c>
       <c r="N172" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="O172" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($200 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($175 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Svedka Vanilla Vodka 1.75L</t>
+          <t>Bombay Gin 1.75L</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>088004071929</t>
+          <t>080480300005</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -11241,22 +11246,22 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F173" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="G173" t="n">
-        <v>-43</v>
+        <v>11</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I173" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K173" t="n">
         <v>12</v>
@@ -11265,127 +11270,127 @@
         <v>2</v>
       </c>
       <c r="M173" t="n">
-        <v>14.62</v>
+        <v>22.13</v>
       </c>
       <c r="N173" t="n">
-        <v>175</v>
+        <v>266</v>
       </c>
       <c r="O173" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($175 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($266 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Bombay Gin 1.75L</t>
+          <t>Crown Royal Peach 750ml</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>080480300005</t>
+          <t>082000782919</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="F174" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="G174" t="n">
-        <v>11</v>
+        <v>-10</v>
       </c>
       <c r="H174" t="n">
-        <v>3.2</v>
+        <v>11.2</v>
       </c>
       <c r="I174" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J174" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K174" t="n">
         <v>12</v>
       </c>
       <c r="L174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>22.13</v>
+        <v>20.21</v>
       </c>
       <c r="N174" t="n">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="O174" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($266 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($243 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Crown Royal Peach 750ml</t>
+          <t>Smirnoff Red White &amp; Berry Liter</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>082000782919</t>
+          <t>082000788096</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="F175" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="G175" t="n">
-        <v>-10</v>
+        <v>-71</v>
       </c>
       <c r="H175" t="n">
-        <v>11.2</v>
+        <v>4.5</v>
       </c>
       <c r="I175" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -11397,13 +11402,13 @@
         <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>20.21</v>
+        <v>10.49</v>
       </c>
       <c r="N175" t="n">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="O175" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr">
@@ -11413,24 +11418,24 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($243 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($126 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Smirnoff Red White &amp; Berry Liter</t>
+          <t>High Noon Peach 8pk 12oz can</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>082000788096</t>
+          <t>085000043073</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Pre-Mix</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11439,113 +11444,113 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F176" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="G176" t="n">
-        <v>-71</v>
+        <v>200</v>
       </c>
       <c r="H176" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I176" t="n">
+        <v>2</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
         <v>9</v>
       </c>
-      <c r="J176" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" t="n">
-        <v>12</v>
-      </c>
       <c r="L176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M176" t="n">
-        <v>10.49</v>
+        <v>16.5</v>
       </c>
       <c r="N176" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="O176" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($126 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($148 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>High Noon Peach 8pk 12oz can</t>
+          <t>Dos Amigos Tequila Blanco 750ml</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>085000043073</t>
+          <t>698450103466</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>New France Wine Co, Inc</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="F177" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="G177" t="n">
-        <v>200</v>
+        <v>-7</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K177" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>16.5</v>
+        <v>18.51</v>
       </c>
       <c r="N177" t="n">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="O177" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>In buy-month (May, Aug, Nov) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($148 to next deal) - confirm</t>
+          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
@@ -12476,83 +12481,83 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Carolans Irish Cream Liter</t>
+          <t>Casamigos Anejo 750ml</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>810845030038</t>
+          <t>856724006015</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="F192" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="G192" t="n">
-        <v>-9</v>
+        <v>-28</v>
       </c>
       <c r="H192" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="I192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L192" t="n">
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>13.68</v>
+        <v>42.01</v>
       </c>
       <c r="N192" t="n">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="O192" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>In buy-month (Mar, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($164 to next deal) - confirm; Seasonal - last year ~13/wk vs 8 now, buy ahead?</t>
+          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Svedka Mango Pineapple Vodka Liter</t>
+          <t>Carolans Irish Cream Liter</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>617768151105</t>
+          <t>810845030038</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12561,19 +12566,19 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F193" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="G193" t="n">
-        <v>-56</v>
+        <v>-9</v>
       </c>
       <c r="H193" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
       <c r="I193" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -12585,40 +12590,40 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>9.42</v>
+        <v>13.68</v>
       </c>
       <c r="N193" t="n">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="O193" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Mar, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($113 to next deal) - confirm; Seasonal - last year ~6/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($164 to next deal) - confirm; Seasonal - last year ~13/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Sauza Hornitos Reposado Tequila Liter</t>
+          <t>Svedka Mango Pineapple Vodka Liter</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>080686835011</t>
+          <t>617768151105</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12627,19 +12632,19 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F194" t="n">
         <v>14.3</v>
       </c>
       <c r="G194" t="n">
-        <v>-70</v>
+        <v>-56</v>
       </c>
       <c r="H194" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -12651,58 +12656,58 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>20.99</v>
+        <v>9.42</v>
       </c>
       <c r="N194" t="n">
-        <v>252</v>
+        <v>113</v>
       </c>
       <c r="O194" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($252 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($113 to next deal) - confirm; Seasonal - last year ~6/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ketel One Botanical Peach &amp; Orange Bloss 750ml</t>
+          <t>Sauza Hornitos Reposado Tequila Liter</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>085156675005</t>
+          <t>080686835011</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F195" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="G195" t="n">
-        <v>-36</v>
+        <v>-70</v>
       </c>
       <c r="H195" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="I195" t="n">
         <v>1</v>
@@ -12717,61 +12722,61 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>14.32</v>
+        <v>20.99</v>
       </c>
       <c r="N195" t="n">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="O195" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, May, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($172 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($252 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Evan Williams Bourbon Liter</t>
+          <t>Ketel One Botanical Peach &amp; Orange Bloss 750ml</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>096749021246</t>
+          <t>085156675005</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="F196" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="G196" t="n">
-        <v>-30</v>
+        <v>-36</v>
       </c>
       <c r="H196" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="I196" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -12783,35 +12788,35 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>11.25</v>
+        <v>14.32</v>
       </c>
       <c r="N196" t="n">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="O196" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($172 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Evan Williams Honey 750ml</t>
+          <t>Evan Williams Bourbon Liter</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>096749021802</t>
+          <t>096749021246</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12825,19 +12830,19 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F197" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="G197" t="n">
-        <v>50</v>
+        <v>-30</v>
       </c>
       <c r="H197" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="I197" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -12849,13 +12854,13 @@
         <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>8.75</v>
+        <v>11.25</v>
       </c>
       <c r="N197" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="O197" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr">
@@ -12865,48 +12870,48 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Gunner Vodka Liter</t>
+          <t>Evan Williams Honey 750ml</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>810879028360</t>
+          <t>096749021802</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="F198" t="n">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="G198" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H198" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="I198" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K198" t="n">
         <v>12</v>
@@ -12915,23 +12920,23 @@
         <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>5.84</v>
+        <v>8.75</v>
       </c>
       <c r="N198" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="O198" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>Overstocked (18 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
         </is>
       </c>
     </row>
@@ -13070,35 +13075,35 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Tip Top Bees Knees 100ml</t>
+          <t>Windsor Apple 1.75L</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>850003799193</t>
+          <t>084279007403</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>360</v>
+        <v>71</v>
       </c>
       <c r="F201" t="n">
-        <v>20.6</v>
+        <v>25.4</v>
       </c>
       <c r="G201" t="n">
-        <v>22</v>
+        <v>-20</v>
       </c>
       <c r="H201" t="n">
-        <v>17</v>
+        <v>3.5</v>
       </c>
       <c r="I201" t="n">
         <v>3</v>
@@ -13107,112 +13112,112 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L201" t="n">
         <v>1</v>
       </c>
       <c r="M201" t="n">
-        <v>3.5</v>
+        <v>15.35</v>
       </c>
       <c r="N201" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="O201" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~17wks to next deal</t>
+        </is>
+      </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Windsor Apple 1.75L</t>
+          <t>Christian Bros Brandy 375ml</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>084279007403</t>
+          <t>086036815672</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F202" t="n">
-        <v>25.4</v>
+        <v>28.1</v>
       </c>
       <c r="G202" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="H202" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L202" t="n">
         <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>15.35</v>
+        <v>4.87</v>
       </c>
       <c r="N202" t="n">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="O202" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~17wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($117 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Christian Bros Brandy 375ml</t>
+          <t>Blackheart Spiced Rum Liter</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>086036815672</t>
+          <t>096749011490</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -13221,16 +13226,16 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F203" t="n">
-        <v>28.1</v>
+        <v>28.9</v>
       </c>
       <c r="G203" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="I203" t="n">
         <v>1</v>
@@ -13239,46 +13244,46 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>4.87</v>
+        <v>10.88</v>
       </c>
       <c r="N203" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="O203" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($117 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($131 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Blackheart Spiced Rum Liter</t>
+          <t>Deep Eddy Lime Liter</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>096749011490</t>
+          <t>856065002264</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -13287,16 +13292,16 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F204" t="n">
-        <v>28.9</v>
+        <v>30</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="H204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I204" t="n">
         <v>1</v>
@@ -13311,13 +13316,13 @@
         <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>10.88</v>
+        <v>14.7</v>
       </c>
       <c r="N204" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="O204" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr">
@@ -13327,42 +13332,42 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($131 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($176 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Deep Eddy Lime Liter</t>
+          <t>Bailey's Chocolate 750ml</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>856065002264</t>
+          <t>086767705488</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F205" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G205" t="n">
-        <v>-50</v>
+        <v>6</v>
       </c>
       <c r="H205" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I205" t="n">
         <v>1</v>
@@ -13377,10 +13382,10 @@
         <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>14.7</v>
+        <v>19.03</v>
       </c>
       <c r="N205" t="n">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="O205" t="n">
         <v>39</v>
@@ -13388,53 +13393,53 @@
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Aug, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($176 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Bailey's Chocolate 750ml</t>
+          <t>Evan Williams Cherry 750ml</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>086767705488</t>
+          <t>096749021857</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F206" t="n">
-        <v>31.2</v>
+        <v>32.7</v>
       </c>
       <c r="G206" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H206" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J206" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K206" t="n">
         <v>12</v>
@@ -13443,35 +13448,35 @@
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>19.03</v>
+        <v>9.57</v>
       </c>
       <c r="N206" t="n">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="O206" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Aug, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Evan Williams Cherry 750ml</t>
+          <t>Jefferson's KY Whisky Reserve 750ml</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>096749021857</t>
+          <t>655709000013</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13485,37 +13490,37 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="F207" t="n">
-        <v>32.7</v>
+        <v>34.3</v>
       </c>
       <c r="G207" t="n">
-        <v>14</v>
+        <v>-65</v>
       </c>
       <c r="H207" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I207" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L207" t="n">
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>9.57</v>
+        <v>42.75</v>
       </c>
       <c r="N207" t="n">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="O207" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
@@ -13525,73 +13530,73 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Jefferson's KY Whisky Reserve 750ml</t>
+          <t>Jose Cuervo Silver Tequila Liter</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>655709000013</t>
+          <t>811538010825</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>16</v>
+        <v>1725</v>
       </c>
       <c r="F208" t="n">
-        <v>34.3</v>
+        <v>38.1</v>
       </c>
       <c r="G208" t="n">
-        <v>-65</v>
+        <v>-2</v>
       </c>
       <c r="H208" t="n">
-        <v>2.5</v>
+        <v>75</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L208" t="n">
         <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>42.75</v>
+        <v>13.97</v>
       </c>
       <c r="N208" t="n">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="O208" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q208" t="inlineStr"/>
-      <c r="R208" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Overstocked (38 wks on hand) - confirm before buying more; Seasonal - last year ~75/wk vs 45 now, buy ahead?</t>
         </is>
       </c>
     </row>
@@ -15629,11 +15634,7 @@
       <c r="O27" t="n">
         <v>16</v>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w)</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
@@ -20396,41 +20397,41 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Gray Duck Liter</t>
+          <t>Bulleit 95 Rye Whiskey 750ml</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>860199002601</t>
+          <t>082000752967</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="F100" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="G100" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H100" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K100" t="n">
         <v>12</v>
@@ -20439,238 +20440,238 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>11.61</v>
+        <v>16.33</v>
       </c>
       <c r="N100" t="n">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="O100" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more; Seasonal - last year ~24/wk vs 11 now, buy ahead?</t>
+          <t>Buy-month stock-up ($196 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bulleit 95 Rye Whiskey 750ml</t>
+          <t>Mi Campo Blanco 750ml</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>082000752967</t>
+          <t>086003272033</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F101" t="n">
         <v>9.9</v>
       </c>
       <c r="G101" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H101" t="n">
-        <v>14.5</v>
+        <v>13.2</v>
       </c>
       <c r="I101" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J101" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M101" t="n">
-        <v>16.33</v>
+        <v>12.47</v>
       </c>
       <c r="N101" t="n">
-        <v>196</v>
+        <v>598</v>
       </c>
       <c r="O101" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($196 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($598 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mi Campo Blanco 750ml</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>086003272033</t>
+          <t>085000434260</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Pre-Mix</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="F102" t="n">
         <v>9.9</v>
       </c>
       <c r="G102" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>13.2</v>
+        <v>8</v>
       </c>
       <c r="I102" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K102" t="n">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="L102" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="M102" t="n">
-        <v>12.47</v>
+        <v>8.25</v>
       </c>
       <c r="N102" t="n">
-        <v>598</v>
+        <v>1584</v>
       </c>
       <c r="O102" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (May, Aug) - stock up ~39wks to next deal</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($598 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,584 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Malibu Black Rum 1.75L</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>085000434260</t>
+          <t>089540520155</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F103" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="H103" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="L103" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>8.25</v>
+        <v>19.67</v>
       </c>
       <c r="N103" t="n">
-        <v>1584</v>
+        <v>118</v>
       </c>
       <c r="O103" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>In buy-month (May, Aug) - stock up ~39wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,584 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($118 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Malibu Black Rum 1.75L</t>
+          <t>Canadian Club Traveler</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>089540520155</t>
+          <t>080686821434</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20679,37 +20680,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="G104" t="n">
-        <v>-33</v>
+        <v>-8</v>
       </c>
       <c r="H104" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="I104" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>24</v>
+      </c>
+      <c r="L104" t="n">
         <v>2</v>
       </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>6</v>
-      </c>
-      <c r="L104" t="n">
-        <v>1</v>
-      </c>
       <c r="M104" t="n">
-        <v>19.67</v>
+        <v>8.15</v>
       </c>
       <c r="N104" t="n">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="O104" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
@@ -20719,42 +20720,42 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($118 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($196 to next deal) - confirm; Seasonal - last year ~11/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Canadian Club Traveler</t>
+          <t>Don Julio Blanco 375ml</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>080686821434</t>
+          <t>674545000599</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F105" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G105" t="n">
-        <v>-8</v>
+        <v>-55</v>
       </c>
       <c r="H105" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="I105" t="n">
         <v>3</v>
@@ -20763,64 +20764,64 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>8.15</v>
+        <v>16.67</v>
       </c>
       <c r="N105" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="O105" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($196 to next deal) - confirm; Seasonal - last year ~11/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($200 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Don Julio Blanco 375ml</t>
+          <t>Svedka Vanilla Vodka 1.75L</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>674545000599</t>
+          <t>088004071929</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F106" t="n">
         <v>10.4</v>
       </c>
       <c r="G106" t="n">
-        <v>-55</v>
+        <v>-43</v>
       </c>
       <c r="H106" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
         <v>3</v>
@@ -20832,43 +20833,43 @@
         <v>12</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M106" t="n">
-        <v>16.67</v>
+        <v>14.62</v>
       </c>
       <c r="N106" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="O106" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($200 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($175 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Svedka Vanilla Vodka 1.75L</t>
+          <t>Bombay Gin 1.75L</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>088004071929</t>
+          <t>080480300005</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Gin</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -20877,22 +20878,22 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F107" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="G107" t="n">
-        <v>-43</v>
+        <v>11</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K107" t="n">
         <v>12</v>
@@ -20901,127 +20902,127 @@
         <v>2</v>
       </c>
       <c r="M107" t="n">
-        <v>14.62</v>
+        <v>22.13</v>
       </c>
       <c r="N107" t="n">
-        <v>175</v>
+        <v>266</v>
       </c>
       <c r="O107" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($175 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($266 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bombay Gin 1.75L</t>
+          <t>Crown Royal Peach 750ml</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>080480300005</t>
+          <t>082000782919</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gin</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="F108" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="G108" t="n">
-        <v>11</v>
+        <v>-10</v>
       </c>
       <c r="H108" t="n">
-        <v>3.2</v>
+        <v>11.2</v>
       </c>
       <c r="I108" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J108" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
         <v>12</v>
       </c>
       <c r="L108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>22.13</v>
+        <v>20.21</v>
       </c>
       <c r="N108" t="n">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="O108" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($266 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($243 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Crown Royal Peach 750ml</t>
+          <t>Smirnoff Red White &amp; Berry Liter</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>082000782919</t>
+          <t>082000788096</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="F109" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="G109" t="n">
-        <v>-10</v>
+        <v>-71</v>
       </c>
       <c r="H109" t="n">
-        <v>11.2</v>
+        <v>4.5</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -21033,13 +21034,13 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>20.21</v>
+        <v>10.49</v>
       </c>
       <c r="N109" t="n">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="O109" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
@@ -21049,24 +21050,24 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($243 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($126 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Smirnoff Red White &amp; Berry Liter</t>
+          <t>High Noon Peach 8pk 12oz can</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>082000788096</t>
+          <t>085000043073</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Pre-Mix</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -21075,113 +21076,113 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F110" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="G110" t="n">
-        <v>-71</v>
+        <v>200</v>
       </c>
       <c r="H110" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
         <v>9</v>
       </c>
-      <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="n">
-        <v>12</v>
-      </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M110" t="n">
-        <v>10.49</v>
+        <v>16.5</v>
       </c>
       <c r="N110" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="O110" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($126 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($148 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>High Noon Peach 8pk 12oz can</t>
+          <t>Dos Amigos Tequila Blanco 750ml</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>085000043073</t>
+          <t>698450103466</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>New France Wine Co, Inc</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="F111" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="G111" t="n">
-        <v>200</v>
+        <v>-7</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K111" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>16.5</v>
+        <v>18.51</v>
       </c>
       <c r="N111" t="n">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="O111" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>In buy-month (May, Aug, Nov) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($148 to next deal) - confirm</t>
+          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
@@ -22112,83 +22113,83 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Carolans Irish Cream Liter</t>
+          <t>Casamigos Anejo 750ml</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>810845030038</t>
+          <t>856724006015</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="F126" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="G126" t="n">
-        <v>-9</v>
+        <v>-28</v>
       </c>
       <c r="H126" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L126" t="n">
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>13.68</v>
+        <v>42.01</v>
       </c>
       <c r="N126" t="n">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="O126" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>In buy-month (Mar, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($164 to next deal) - confirm; Seasonal - last year ~13/wk vs 8 now, buy ahead?</t>
+          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Svedka Mango Pineapple Vodka Liter</t>
+          <t>Carolans Irish Cream Liter</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>617768151105</t>
+          <t>810845030038</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -22197,19 +22198,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="F127" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="G127" t="n">
-        <v>-56</v>
+        <v>-9</v>
       </c>
       <c r="H127" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -22221,40 +22222,40 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>9.42</v>
+        <v>13.68</v>
       </c>
       <c r="N127" t="n">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="O127" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Mar, Jun, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($113 to next deal) - confirm; Seasonal - last year ~6/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($164 to next deal) - confirm; Seasonal - last year ~13/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sauza Hornitos Reposado Tequila Liter</t>
+          <t>Svedka Mango Pineapple Vodka Liter</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>080686835011</t>
+          <t>617768151105</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Agave</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -22263,19 +22264,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F128" t="n">
         <v>14.3</v>
       </c>
       <c r="G128" t="n">
-        <v>-70</v>
+        <v>-56</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -22287,58 +22288,58 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>20.99</v>
+        <v>9.42</v>
       </c>
       <c r="N128" t="n">
-        <v>252</v>
+        <v>113</v>
       </c>
       <c r="O128" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($252 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($113 to next deal) - confirm; Seasonal - last year ~6/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ketel One Botanical Peach &amp; Orange Bloss 750ml</t>
+          <t>Sauza Hornitos Reposado Tequila Liter</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>085156675005</t>
+          <t>080686835011</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F129" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="G129" t="n">
-        <v>-36</v>
+        <v>-70</v>
       </c>
       <c r="H129" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -22353,61 +22354,61 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>14.32</v>
+        <v>20.99</v>
       </c>
       <c r="N129" t="n">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="O129" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, May, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($172 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($252 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Evan Williams Bourbon Liter</t>
+          <t>Ketel One Botanical Peach &amp; Orange Bloss 750ml</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>096749021246</t>
+          <t>085156675005</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="F130" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="G130" t="n">
-        <v>-30</v>
+        <v>-36</v>
       </c>
       <c r="H130" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="I130" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -22419,35 +22420,35 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>11.25</v>
+        <v>14.32</v>
       </c>
       <c r="N130" t="n">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="O130" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($172 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Evan Williams Honey 750ml</t>
+          <t>Evan Williams Bourbon Liter</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>096749021802</t>
+          <t>096749021246</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -22461,19 +22462,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F131" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="G131" t="n">
-        <v>50</v>
+        <v>-30</v>
       </c>
       <c r="H131" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -22485,13 +22486,13 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>8.75</v>
+        <v>11.25</v>
       </c>
       <c r="N131" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="O131" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
@@ -22501,48 +22502,48 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Gunner Vodka Liter</t>
+          <t>Evan Williams Honey 750ml</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>810879028360</t>
+          <t>096749021802</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="F132" t="n">
-        <v>18</v>
+        <v>16.7</v>
       </c>
       <c r="G132" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H132" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="I132" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
         <v>12</v>
@@ -22551,23 +22552,23 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>5.84</v>
+        <v>8.75</v>
       </c>
       <c r="N132" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="O132" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Overstocked (18 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
         </is>
       </c>
     </row>
@@ -22706,35 +22707,35 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Tip Top Bees Knees 100ml</t>
+          <t>Windsor Apple 1.75L</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>850003799193</t>
+          <t>084279007403</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pre-Mix</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>360</v>
+        <v>71</v>
       </c>
       <c r="F135" t="n">
-        <v>20.6</v>
+        <v>25.4</v>
       </c>
       <c r="G135" t="n">
-        <v>22</v>
+        <v>-20</v>
       </c>
       <c r="H135" t="n">
-        <v>17</v>
+        <v>3.5</v>
       </c>
       <c r="I135" t="n">
         <v>3</v>
@@ -22743,112 +22744,112 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>3.5</v>
+        <v>15.35</v>
       </c>
       <c r="N135" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="O135" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~17wks to next deal</t>
+        </is>
+      </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Windsor Apple 1.75L</t>
+          <t>Christian Bros Brandy 375ml</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>084279007403</t>
+          <t>086036815672</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F136" t="n">
-        <v>25.4</v>
+        <v>28.1</v>
       </c>
       <c r="G136" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="H136" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L136" t="n">
         <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>15.35</v>
+        <v>4.87</v>
       </c>
       <c r="N136" t="n">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="O136" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Mar, Apr, May, Jun, Jul, Aug, Dec) - stock up ~17wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($117 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Christian Bros Brandy 375ml</t>
+          <t>Blackheart Spiced Rum Liter</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>086036815672</t>
+          <t>096749011490</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Rum</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22857,16 +22858,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F137" t="n">
-        <v>28.1</v>
+        <v>28.9</v>
       </c>
       <c r="G137" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="I137" t="n">
         <v>1</v>
@@ -22875,46 +22876,46 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>4.87</v>
+        <v>10.88</v>
       </c>
       <c r="N137" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="O137" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($117 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($131 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Blackheart Spiced Rum Liter</t>
+          <t>Deep Eddy Lime Liter</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>096749011490</t>
+          <t>856065002264</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Rum</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22923,16 +22924,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F138" t="n">
-        <v>28.9</v>
+        <v>30</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="H138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I138" t="n">
         <v>1</v>
@@ -22947,13 +22948,13 @@
         <v>1</v>
       </c>
       <c r="M138" t="n">
-        <v>10.88</v>
+        <v>14.7</v>
       </c>
       <c r="N138" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="O138" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
@@ -22963,42 +22964,42 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($131 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($176 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Deep Eddy Lime Liter</t>
+          <t>Bailey's Chocolate 750ml</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>856065002264</t>
+          <t>086767705488</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Cordials</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F139" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G139" t="n">
-        <v>-50</v>
+        <v>6</v>
       </c>
       <c r="H139" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -23013,10 +23014,10 @@
         <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>14.7</v>
+        <v>19.03</v>
       </c>
       <c r="N139" t="n">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="O139" t="n">
         <v>39</v>
@@ -23024,53 +23025,53 @@
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Aug, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($176 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Bailey's Chocolate 750ml</t>
+          <t>Evan Williams Cherry 750ml</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>086767705488</t>
+          <t>096749021857</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cordials</t>
+          <t>Whisky/Whiskey</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F140" t="n">
-        <v>31.2</v>
+        <v>32.7</v>
       </c>
       <c r="G140" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H140" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K140" t="n">
         <v>12</v>
@@ -23079,35 +23080,35 @@
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>19.03</v>
+        <v>9.57</v>
       </c>
       <c r="N140" t="n">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="O140" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Aug, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($228 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Evan Williams Cherry 750ml</t>
+          <t>Jefferson's KY Whisky Reserve 750ml</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>096749021857</t>
+          <t>655709000013</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -23121,37 +23122,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="F141" t="n">
-        <v>32.7</v>
+        <v>34.3</v>
       </c>
       <c r="G141" t="n">
-        <v>14</v>
+        <v>-65</v>
       </c>
       <c r="H141" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="I141" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L141" t="n">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>9.57</v>
+        <v>42.75</v>
       </c>
       <c r="N141" t="n">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="O141" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
@@ -23161,73 +23162,73 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($115 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Jefferson's KY Whisky Reserve 750ml</t>
+          <t>Jose Cuervo Silver Tequila Liter</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>655709000013</t>
+          <t>811538010825</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Whisky/Whiskey</t>
+          <t>Agave</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>16</v>
+        <v>1725</v>
       </c>
       <c r="F142" t="n">
-        <v>34.3</v>
+        <v>38.1</v>
       </c>
       <c r="G142" t="n">
-        <v>-65</v>
+        <v>-2</v>
       </c>
       <c r="H142" t="n">
-        <v>2.5</v>
+        <v>75</v>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>42.75</v>
+        <v>13.97</v>
       </c>
       <c r="N142" t="n">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="O142" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 8w)</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($256 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Overstocked (38 wks on hand) - confirm before buying more; Seasonal - last year ~75/wk vs 45 now, buy ahead?</t>
         </is>
       </c>
     </row>
